--- a/research/traditional_assets/database/data/bermuda/bermuda_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_precious_metals.xlsx
@@ -1133,43 +1133,43 @@
         <v>91.1538461538462</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>102.48237389652</v>
       </c>
       <c r="G2">
         <v>0.080695652173913</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.119937391304348</v>
       </c>
       <c r="I2">
         <v>0.00672814801925642</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>137</v>
       </c>
       <c r="L2">
-        <v>138.013412441277</v>
+        <v>136.602141904805</v>
       </c>
       <c r="M2">
         <v>40.128</v>
       </c>
       <c r="N2">
-        <v>40.2134124412771</v>
+        <v>40.181421904805</v>
       </c>
       <c r="O2">
         <v>0.928</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.37928</v>
       </c>
       <c r="Q2">
         <v>0.102442146780926</v>
       </c>
       <c r="R2">
-        <v>0.102321840053841</v>
+        <v>0.102366840053841</v>
       </c>
       <c r="S2">
         <v>0.06368110587651871</v>
@@ -1191,13 +1191,13 @@
         <v>0.102704703320775</v>
       </c>
       <c r="X2">
-        <v>0.102321840053841</v>
+        <v>0.102892767731152</v>
       </c>
       <c r="Y2">
         <v>1.04222962542635</v>
       </c>
       <c r="Z2">
-        <v>1.03521735023643</v>
+        <v>1.04567409114791</v>
       </c>
       <c r="AA2">
         <v>0.928</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1023218400538407</v>
+        <v>0.1023668400538408</v>
       </c>
       <c r="C2">
-        <v>138.0134124412771</v>
+        <v>136.602141904805</v>
       </c>
       <c r="D2">
-        <v>40.21341244127714</v>
+        <v>40.18142190480498</v>
       </c>
       <c r="E2">
-        <v>-0.928</v>
+        <v>0.45128</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.37928</v>
       </c>
       <c r="G2">
         <v>97.8</v>
@@ -1451,28 +1451,28 @@
         <v>7.11</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.069377784</v>
       </c>
       <c r="N2">
-        <v>7.11</v>
+        <v>7.040622216</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>7.11</v>
+        <v>7.040622216</v>
       </c>
       <c r="Q2">
-        <v>11.5</v>
+        <v>11.430622216</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1023218400538407</v>
+        <v>0.1028927677311523</v>
       </c>
       <c r="T2">
-        <v>1.035217350236429</v>
+        <v>1.045674091147908</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>102.48237389652</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1023668400538408</v>
+        <v>0.1024118400538407</v>
       </c>
       <c r="C3">
-        <v>136.602141904805</v>
+        <v>135.1909222260382</v>
       </c>
       <c r="D3">
-        <v>40.18142190480498</v>
+        <v>40.1494822260382</v>
       </c>
       <c r="E3">
-        <v>0.45128</v>
+        <v>1.83056</v>
       </c>
       <c r="F3">
-        <v>1.37928</v>
+        <v>2.75856</v>
       </c>
       <c r="G3">
         <v>97.8</v>
@@ -1533,28 +1533,28 @@
         <v>7.11</v>
       </c>
       <c r="M3">
-        <v>0.069377784</v>
+        <v>0.138755568</v>
       </c>
       <c r="N3">
-        <v>7.040622216</v>
+        <v>6.971244432000001</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>7.040622216</v>
+        <v>6.971244432000001</v>
       </c>
       <c r="Q3">
-        <v>11.430622216</v>
+        <v>11.361244432</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1028927677311523</v>
+        <v>0.1034753469937151</v>
       </c>
       <c r="T3">
-        <v>1.045674091147908</v>
+        <v>1.056344234935132</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>102.48237389652</v>
+        <v>51.24118694825999</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1024118400538407</v>
+        <v>0.1024568400538407</v>
       </c>
       <c r="C4">
-        <v>135.1909222260382</v>
+        <v>133.7797532837948</v>
       </c>
       <c r="D4">
-        <v>40.1494822260382</v>
+        <v>40.11759328379479</v>
       </c>
       <c r="E4">
-        <v>1.83056</v>
+        <v>3.20984</v>
       </c>
       <c r="F4">
-        <v>2.75856</v>
+        <v>4.13784</v>
       </c>
       <c r="G4">
         <v>97.8</v>
@@ -1615,28 +1615,28 @@
         <v>7.11</v>
       </c>
       <c r="M4">
-        <v>0.138755568</v>
+        <v>0.208133352</v>
       </c>
       <c r="N4">
-        <v>6.971244432000001</v>
+        <v>6.901866648</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>6.971244432000001</v>
+        <v>6.901866648</v>
       </c>
       <c r="Q4">
-        <v>11.361244432</v>
+        <v>11.291866648</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1034753469937151</v>
+        <v>0.1040699381998358</v>
       </c>
       <c r="T4">
-        <v>1.056344234935132</v>
+        <v>1.06723438168704</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>51.24118694825999</v>
+        <v>34.16079129884</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1024568400538407</v>
+        <v>0.1025018400538407</v>
       </c>
       <c r="C5">
-        <v>133.7797532837948</v>
+        <v>132.3686349572774</v>
       </c>
       <c r="D5">
-        <v>40.11759328379479</v>
+        <v>40.08575495727739</v>
       </c>
       <c r="E5">
-        <v>3.20984</v>
+        <v>4.58912</v>
       </c>
       <c r="F5">
-        <v>4.13784</v>
+        <v>5.51712</v>
       </c>
       <c r="G5">
         <v>97.8</v>
@@ -1697,28 +1697,28 @@
         <v>7.11</v>
       </c>
       <c r="M5">
-        <v>0.208133352</v>
+        <v>0.277511136</v>
       </c>
       <c r="N5">
-        <v>6.901866648</v>
+        <v>6.832488864</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>6.901866648</v>
+        <v>6.832488864</v>
       </c>
       <c r="Q5">
-        <v>11.291866648</v>
+        <v>11.222488864</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1040699381998358</v>
+        <v>0.1046769167227508</v>
       </c>
       <c r="T5">
-        <v>1.06723438168704</v>
+        <v>1.07835140649628</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.16079129884</v>
+        <v>25.62059347412999</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1025018400538407</v>
+        <v>0.1025468400538408</v>
       </c>
       <c r="C6">
-        <v>132.3686349572774</v>
+        <v>130.9575671260719</v>
       </c>
       <c r="D6">
-        <v>40.08575495727739</v>
+        <v>40.05396712607188</v>
       </c>
       <c r="E6">
-        <v>4.58912</v>
+        <v>5.9684</v>
       </c>
       <c r="F6">
-        <v>5.51712</v>
+        <v>6.8964</v>
       </c>
       <c r="G6">
         <v>97.8</v>
@@ -1779,28 +1779,28 @@
         <v>7.11</v>
       </c>
       <c r="M6">
-        <v>0.277511136</v>
+        <v>0.34688892</v>
       </c>
       <c r="N6">
-        <v>6.832488864</v>
+        <v>6.763111080000001</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>6.832488864</v>
+        <v>6.763111080000001</v>
       </c>
       <c r="Q6">
-        <v>11.222488864</v>
+        <v>11.15311108</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1046769167227508</v>
+        <v>0.105296673740885</v>
       </c>
       <c r="T6">
-        <v>1.07835140649628</v>
+        <v>1.089702473933083</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.62059347412999</v>
+        <v>20.49647477930399</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1025468400538408</v>
+        <v>0.1025918400538407</v>
       </c>
       <c r="C7">
-        <v>130.9575671260719</v>
+        <v>129.5465496701457</v>
       </c>
       <c r="D7">
-        <v>40.05396712607188</v>
+        <v>40.02222967014574</v>
       </c>
       <c r="E7">
-        <v>5.9684</v>
+        <v>7.347680000000001</v>
       </c>
       <c r="F7">
-        <v>6.8964</v>
+        <v>8.275680000000001</v>
       </c>
       <c r="G7">
         <v>97.8</v>
@@ -1861,28 +1861,28 @@
         <v>7.11</v>
       </c>
       <c r="M7">
-        <v>0.34688892</v>
+        <v>0.416266704</v>
       </c>
       <c r="N7">
-        <v>6.763111080000001</v>
+        <v>6.693733296</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>6.763111080000001</v>
+        <v>6.693733296</v>
       </c>
       <c r="Q7">
-        <v>11.15311108</v>
+        <v>11.083733296</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.105296673740885</v>
+        <v>0.105929617078554</v>
       </c>
       <c r="T7">
-        <v>1.089702473933083</v>
+        <v>1.101295053443009</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.49647477930399</v>
+        <v>17.08039564941999</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1025918400538407</v>
+        <v>0.1026368400538407</v>
       </c>
       <c r="C8">
-        <v>129.5465496701458</v>
+        <v>128.1355824698466</v>
       </c>
       <c r="D8">
-        <v>40.02222967014576</v>
+        <v>39.99054246984659</v>
       </c>
       <c r="E8">
-        <v>7.34768</v>
+        <v>8.726959999999998</v>
       </c>
       <c r="F8">
-        <v>8.275679999999999</v>
+        <v>9.654959999999999</v>
       </c>
       <c r="G8">
         <v>97.8</v>
@@ -1943,28 +1943,28 @@
         <v>7.11</v>
       </c>
       <c r="M8">
-        <v>0.4162667039999999</v>
+        <v>0.4856444879999999</v>
       </c>
       <c r="N8">
-        <v>6.693733296</v>
+        <v>6.624355512</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>6.693733296</v>
+        <v>6.624355512</v>
       </c>
       <c r="Q8">
-        <v>11.083733296</v>
+        <v>11.014355512</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.105929617078554</v>
+        <v>0.106576172100904</v>
       </c>
       <c r="T8">
-        <v>1.101295053443009</v>
+        <v>1.113136935738096</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.08039564942</v>
+        <v>14.64033912807428</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1026368400538407</v>
+        <v>0.1028018400538407</v>
       </c>
       <c r="C9">
-        <v>128.1355824698466</v>
+        <v>126.6405441100938</v>
       </c>
       <c r="D9">
-        <v>39.99054246984659</v>
+        <v>39.87478411009378</v>
       </c>
       <c r="E9">
-        <v>8.72696</v>
+        <v>10.10624</v>
       </c>
       <c r="F9">
-        <v>9.654960000000001</v>
+        <v>11.03424</v>
       </c>
       <c r="G9">
         <v>97.8</v>
@@ -2025,45 +2025,45 @@
         <v>7.11</v>
       </c>
       <c r="M9">
-        <v>0.485644488</v>
+        <v>0.571573632</v>
       </c>
       <c r="N9">
-        <v>6.624355512</v>
+        <v>6.538426368000001</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>6.624355512</v>
+        <v>6.538426368000001</v>
       </c>
       <c r="Q9">
-        <v>11.014355512</v>
+        <v>10.928426368</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.106576172100904</v>
+        <v>0.1072367826672182</v>
       </c>
       <c r="T9">
-        <v>1.113136935738096</v>
+        <v>1.125236250256988</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.64033912807428</v>
+        <v>12.4393421983469</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1028018400538407</v>
+        <v>0.1028618400538408</v>
       </c>
       <c r="C10">
-        <v>126.6405441100938</v>
+        <v>125.2193361413436</v>
       </c>
       <c r="D10">
-        <v>39.87478411009378</v>
+        <v>39.83285614134358</v>
       </c>
       <c r="E10">
-        <v>10.10624</v>
+        <v>11.48552</v>
       </c>
       <c r="F10">
-        <v>11.03424</v>
+        <v>12.41352</v>
       </c>
       <c r="G10">
         <v>97.8</v>
@@ -2107,28 +2107,28 @@
         <v>7.11</v>
       </c>
       <c r="M10">
-        <v>0.571573632</v>
+        <v>0.643020336</v>
       </c>
       <c r="N10">
-        <v>6.538426368000001</v>
+        <v>6.466979664</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>6.538426368000001</v>
+        <v>6.466979664</v>
       </c>
       <c r="Q10">
-        <v>10.928426368</v>
+        <v>10.856979664</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1072367826672182</v>
+        <v>0.1079119121470778</v>
       </c>
       <c r="T10">
-        <v>1.125236250256988</v>
+        <v>1.137601483776296</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.4393421983469</v>
+        <v>11.05719306519724</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1028618400538408</v>
+        <v>0.1029218400538408</v>
       </c>
       <c r="C11">
-        <v>125.2193361413436</v>
+        <v>123.7982162537239</v>
       </c>
       <c r="D11">
-        <v>39.83285614134358</v>
+        <v>39.79101625372394</v>
       </c>
       <c r="E11">
-        <v>11.48552</v>
+        <v>12.8648</v>
       </c>
       <c r="F11">
-        <v>12.41352</v>
+        <v>13.7928</v>
       </c>
       <c r="G11">
         <v>97.8</v>
@@ -2189,28 +2189,28 @@
         <v>7.11</v>
       </c>
       <c r="M11">
-        <v>0.643020336</v>
+        <v>0.7144670399999998</v>
       </c>
       <c r="N11">
-        <v>6.466979664</v>
+        <v>6.395532960000001</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>6.466979664</v>
+        <v>6.395532960000001</v>
       </c>
       <c r="Q11">
-        <v>10.856979664</v>
+        <v>10.78553296</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1079119121470778</v>
+        <v>0.1086020445042675</v>
       </c>
       <c r="T11">
-        <v>1.137601483776296</v>
+        <v>1.150241500262699</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.05719306519724</v>
+        <v>9.951473758677521</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1029218400538408</v>
+        <v>0.1031688400538408</v>
       </c>
       <c r="C12">
-        <v>123.7982162537239</v>
+        <v>122.2476171019781</v>
       </c>
       <c r="D12">
-        <v>39.79101625372394</v>
+        <v>39.61969710197804</v>
       </c>
       <c r="E12">
-        <v>12.8648</v>
+        <v>14.24408</v>
       </c>
       <c r="F12">
-        <v>13.7928</v>
+        <v>15.17208</v>
       </c>
       <c r="G12">
         <v>97.8</v>
@@ -2271,45 +2271,45 @@
         <v>7.11</v>
       </c>
       <c r="M12">
-        <v>0.7144670399999999</v>
+        <v>0.81170628</v>
       </c>
       <c r="N12">
-        <v>6.395532960000001</v>
+        <v>6.29829372</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>6.395532960000001</v>
+        <v>6.29829372</v>
       </c>
       <c r="Q12">
-        <v>10.78553296</v>
+        <v>10.68829372</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1086020445042675</v>
+        <v>0.1093076854537537</v>
       </c>
       <c r="T12">
-        <v>1.150241500262699</v>
+        <v>1.163165562063403</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>9.951473758677519</v>
+        <v>8.759326095148605</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1031688400538408</v>
+        <v>0.1032458400538407</v>
       </c>
       <c r="C13">
-        <v>122.2476171019781</v>
+        <v>120.8152311386221</v>
       </c>
       <c r="D13">
-        <v>39.61969710197804</v>
+        <v>39.56659113862209</v>
       </c>
       <c r="E13">
-        <v>14.24408</v>
+        <v>15.62336</v>
       </c>
       <c r="F13">
-        <v>15.17208</v>
+        <v>16.55136</v>
       </c>
       <c r="G13">
         <v>97.8</v>
@@ -2353,28 +2353,28 @@
         <v>7.11</v>
       </c>
       <c r="M13">
-        <v>0.81170628</v>
+        <v>0.8854977599999999</v>
       </c>
       <c r="N13">
-        <v>6.29829372</v>
+        <v>6.224502240000001</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>6.29829372</v>
+        <v>6.224502240000001</v>
       </c>
       <c r="Q13">
-        <v>10.68829372</v>
+        <v>10.61450224</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1093076854537537</v>
+        <v>0.1100293636975463</v>
       </c>
       <c r="T13">
-        <v>1.163165562063403</v>
+        <v>1.176383352541396</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.759326095148605</v>
+        <v>8.029382253886222</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1032458400538407</v>
+        <v>0.1034268400538408</v>
       </c>
       <c r="C14">
-        <v>120.8152311386221</v>
+        <v>119.3116765299606</v>
       </c>
       <c r="D14">
-        <v>39.56659113862209</v>
+        <v>39.44231652996056</v>
       </c>
       <c r="E14">
-        <v>15.62336</v>
+        <v>17.00264</v>
       </c>
       <c r="F14">
-        <v>16.55136</v>
+        <v>17.93064</v>
       </c>
       <c r="G14">
         <v>97.8</v>
@@ -2435,45 +2435,45 @@
         <v>7.11</v>
       </c>
       <c r="M14">
-        <v>0.8854977599999999</v>
+        <v>0.973633752</v>
       </c>
       <c r="N14">
-        <v>6.224502240000001</v>
+        <v>6.136366248</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>6.224502240000001</v>
+        <v>6.136366248</v>
       </c>
       <c r="Q14">
-        <v>10.61450224</v>
+        <v>10.526366248</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1100293636975463</v>
+        <v>0.110767632245794</v>
       </c>
       <c r="T14">
-        <v>1.176383352541396</v>
+        <v>1.189905000271757</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.029382253886222</v>
+        <v>7.302540596394608</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1034268400538408</v>
+        <v>0.1035118400538407</v>
       </c>
       <c r="C15">
-        <v>119.3116765299606</v>
+        <v>117.8743045179589</v>
       </c>
       <c r="D15">
-        <v>39.44231652996056</v>
+        <v>39.38422451795889</v>
       </c>
       <c r="E15">
-        <v>17.00264</v>
+        <v>18.38192</v>
       </c>
       <c r="F15">
-        <v>17.93064</v>
+        <v>19.30992</v>
       </c>
       <c r="G15">
         <v>97.8</v>
@@ -2517,28 +2517,28 @@
         <v>7.11</v>
       </c>
       <c r="M15">
-        <v>0.973633752</v>
+        <v>1.048528656</v>
       </c>
       <c r="N15">
-        <v>6.136366248</v>
+        <v>6.061471344</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>6.136366248</v>
+        <v>6.061471344</v>
       </c>
       <c r="Q15">
-        <v>10.526366248</v>
+        <v>10.451471344</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.110767632245794</v>
+        <v>0.1115230698300474</v>
       </c>
       <c r="T15">
-        <v>1.189905000271757</v>
+        <v>1.20374110492608</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.302540596394608</v>
+        <v>6.780930553794992</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1035118400538407</v>
+        <v>0.1035968400538407</v>
       </c>
       <c r="C16">
-        <v>117.8743045179589</v>
+        <v>116.4371033741575</v>
       </c>
       <c r="D16">
-        <v>39.38422451795889</v>
+        <v>39.32630337415746</v>
       </c>
       <c r="E16">
-        <v>18.38192</v>
+        <v>19.7612</v>
       </c>
       <c r="F16">
-        <v>19.30992</v>
+        <v>20.6892</v>
       </c>
       <c r="G16">
         <v>97.8</v>
@@ -2599,28 +2599,28 @@
         <v>7.11</v>
       </c>
       <c r="M16">
-        <v>1.048528656</v>
+        <v>1.12342356</v>
       </c>
       <c r="N16">
-        <v>6.061471344</v>
+        <v>5.98657644</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>6.061471344</v>
+        <v>5.98657644</v>
       </c>
       <c r="Q16">
-        <v>10.451471344</v>
+        <v>10.37657644</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1115230698300474</v>
+        <v>0.1122962824162832</v>
       </c>
       <c r="T16">
-        <v>1.20374110492608</v>
+        <v>1.217902764984034</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.780930553794992</v>
+        <v>6.328868516875326</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1035968400538407</v>
+        <v>0.1038418400538407</v>
       </c>
       <c r="C17">
-        <v>116.4371033741575</v>
+        <v>114.891823393493</v>
       </c>
       <c r="D17">
-        <v>39.32630337415746</v>
+        <v>39.16030339349298</v>
       </c>
       <c r="E17">
-        <v>19.7612</v>
+        <v>21.14048</v>
       </c>
       <c r="F17">
-        <v>20.6892</v>
+        <v>22.06848</v>
       </c>
       <c r="G17">
         <v>97.8</v>
@@ -2681,45 +2681,45 @@
         <v>7.11</v>
       </c>
       <c r="M17">
-        <v>1.12342356</v>
+        <v>1.220386944</v>
       </c>
       <c r="N17">
-        <v>5.98657644</v>
+        <v>5.889613056</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>5.98657644</v>
+        <v>5.889613056</v>
       </c>
       <c r="Q17">
-        <v>10.37657644</v>
+        <v>10.279613056</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1122962824162832</v>
+        <v>0.1130879048260009</v>
       </c>
       <c r="T17">
-        <v>1.217902764984034</v>
+        <v>1.23240160742432</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.328868516875327</v>
+        <v>5.826021029605508</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1038418400538407</v>
+        <v>0.1039368400538407</v>
       </c>
       <c r="C18">
-        <v>114.891823393493</v>
+        <v>113.448552491701</v>
       </c>
       <c r="D18">
-        <v>39.16030339349298</v>
+        <v>39.09631249170099</v>
       </c>
       <c r="E18">
-        <v>21.14048</v>
+        <v>22.51976</v>
       </c>
       <c r="F18">
-        <v>22.06848</v>
+        <v>23.44776</v>
       </c>
       <c r="G18">
         <v>97.8</v>
@@ -2763,28 +2763,28 @@
         <v>7.11</v>
       </c>
       <c r="M18">
-        <v>1.220386944</v>
+        <v>1.296661128</v>
       </c>
       <c r="N18">
-        <v>5.889613056</v>
+        <v>5.813338872</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>5.889613056</v>
+        <v>5.813338872</v>
       </c>
       <c r="Q18">
-        <v>10.279613056</v>
+        <v>10.203338872</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1130879048260009</v>
+        <v>0.1138986024745069</v>
       </c>
       <c r="T18">
-        <v>1.23240160742432</v>
+        <v>1.247249819561963</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.826021029605508</v>
+        <v>5.483313910216949</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1039368400538407</v>
+        <v>0.1040318400538408</v>
       </c>
       <c r="C19">
-        <v>113.448552491701</v>
+        <v>112.0054903806896</v>
       </c>
       <c r="D19">
-        <v>39.09631249170099</v>
+        <v>39.03253038068959</v>
       </c>
       <c r="E19">
-        <v>22.51976</v>
+        <v>23.89904</v>
       </c>
       <c r="F19">
-        <v>23.44776</v>
+        <v>24.82704</v>
       </c>
       <c r="G19">
         <v>97.8</v>
@@ -2845,28 +2845,28 @@
         <v>7.11</v>
       </c>
       <c r="M19">
-        <v>1.296661128</v>
+        <v>1.372935312</v>
       </c>
       <c r="N19">
-        <v>5.813338872</v>
+        <v>5.737064688</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>5.813338872</v>
+        <v>5.737064688</v>
       </c>
       <c r="Q19">
-        <v>10.203338872</v>
+        <v>10.127064688</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1138986024745069</v>
+        <v>0.1147290732363912</v>
       </c>
       <c r="T19">
-        <v>1.247249819561963</v>
+        <v>1.262460183215157</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.483313910216949</v>
+        <v>5.17868535964934</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1040318400538408</v>
+        <v>0.1041268400538407</v>
       </c>
       <c r="C20">
-        <v>112.0054903806896</v>
+        <v>110.5626360402531</v>
       </c>
       <c r="D20">
-        <v>39.03253038068959</v>
+        <v>38.96895604025314</v>
       </c>
       <c r="E20">
-        <v>23.89904</v>
+        <v>25.27832</v>
       </c>
       <c r="F20">
-        <v>24.82704</v>
+        <v>26.20632</v>
       </c>
       <c r="G20">
         <v>97.8</v>
@@ -2927,28 +2927,28 @@
         <v>7.11</v>
       </c>
       <c r="M20">
-        <v>1.372935312</v>
+        <v>1.449209496</v>
       </c>
       <c r="N20">
-        <v>5.737064688</v>
+        <v>5.660790504</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>5.737064688</v>
+        <v>5.660790504</v>
       </c>
       <c r="Q20">
-        <v>10.127064688</v>
+        <v>10.050790504</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1147290732363912</v>
+        <v>0.1155800494491861</v>
       </c>
       <c r="T20">
-        <v>1.262460183215157</v>
+        <v>1.278046111402999</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.178685359649341</v>
+        <v>4.906122972299376</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1041268400538407</v>
+        <v>0.1042218400538408</v>
       </c>
       <c r="C21">
-        <v>110.5626360402531</v>
+        <v>109.1199884568218</v>
       </c>
       <c r="D21">
-        <v>38.96895604025314</v>
+        <v>38.9055884568218</v>
       </c>
       <c r="E21">
-        <v>25.27832</v>
+        <v>26.6576</v>
       </c>
       <c r="F21">
-        <v>26.20632</v>
+        <v>27.5856</v>
       </c>
       <c r="G21">
         <v>97.8</v>
@@ -3009,28 +3009,28 @@
         <v>7.11</v>
       </c>
       <c r="M21">
-        <v>1.449209496</v>
+        <v>1.52548368</v>
       </c>
       <c r="N21">
-        <v>5.660790504</v>
+        <v>5.584516320000001</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>5.660790504</v>
+        <v>5.584516320000001</v>
       </c>
       <c r="Q21">
-        <v>10.050790504</v>
+        <v>9.974516319999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1155800494491861</v>
+        <v>0.116452300067301</v>
       </c>
       <c r="T21">
-        <v>1.278046111402999</v>
+        <v>1.294021687795536</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.906122972299376</v>
+        <v>4.660816823684407</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1042218400538408</v>
+        <v>0.1048418400538408</v>
       </c>
       <c r="C22">
-        <v>109.1199884568218</v>
+        <v>107.3321597933446</v>
       </c>
       <c r="D22">
-        <v>38.9055884568218</v>
+        <v>38.49703979334463</v>
       </c>
       <c r="E22">
-        <v>26.6576</v>
+        <v>28.03688</v>
       </c>
       <c r="F22">
-        <v>27.5856</v>
+        <v>28.96488</v>
       </c>
       <c r="G22">
         <v>97.8</v>
@@ -3091,45 +3091,45 @@
         <v>7.11</v>
       </c>
       <c r="M22">
-        <v>1.52548368</v>
+        <v>1.674170064</v>
       </c>
       <c r="N22">
-        <v>5.584516320000001</v>
+        <v>5.435829936</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>5.584516320000001</v>
+        <v>5.435829936</v>
       </c>
       <c r="Q22">
-        <v>9.974516319999999</v>
+        <v>9.825829936</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.116452300067301</v>
+        <v>0.1173466329795453</v>
       </c>
       <c r="T22">
-        <v>1.294021687795536</v>
+        <v>1.310401709160037</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.660816823684407</v>
+        <v>4.246880381442539</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1048418400538408</v>
+        <v>0.1049618400538408</v>
       </c>
       <c r="C23">
-        <v>107.3321597933446</v>
+        <v>105.8747949202068</v>
       </c>
       <c r="D23">
-        <v>38.49703979334463</v>
+        <v>38.41895492020686</v>
       </c>
       <c r="E23">
-        <v>28.03688</v>
+        <v>29.41616</v>
       </c>
       <c r="F23">
-        <v>28.96488</v>
+        <v>30.34416</v>
       </c>
       <c r="G23">
         <v>97.8</v>
@@ -3173,28 +3173,28 @@
         <v>7.11</v>
       </c>
       <c r="M23">
-        <v>1.674170064</v>
+        <v>1.753892448</v>
       </c>
       <c r="N23">
-        <v>5.435829936</v>
+        <v>5.356107552</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>5.435829936</v>
+        <v>5.356107552</v>
       </c>
       <c r="Q23">
-        <v>9.825829936</v>
+        <v>9.746107552</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1173466329795453</v>
+        <v>0.118263897504924</v>
       </c>
       <c r="T23">
-        <v>1.310401709160037</v>
+        <v>1.327201731072345</v>
       </c>
       <c r="U23">
         <v>0.0578</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.246880381442539</v>
+        <v>4.053840364104242</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1049618400538408</v>
+        <v>0.1058868400538407</v>
       </c>
       <c r="C24">
-        <v>105.8747949202068</v>
+        <v>103.9040787044007</v>
       </c>
       <c r="D24">
-        <v>38.41895492020686</v>
+        <v>37.82751870440074</v>
       </c>
       <c r="E24">
-        <v>29.41616</v>
+        <v>30.79544</v>
       </c>
       <c r="F24">
-        <v>30.34416</v>
+        <v>31.72344</v>
       </c>
       <c r="G24">
         <v>97.8</v>
@@ -3255,45 +3255,45 @@
         <v>7.11</v>
       </c>
       <c r="M24">
-        <v>1.753892448</v>
+        <v>1.944646872</v>
       </c>
       <c r="N24">
-        <v>5.356107552</v>
+        <v>5.165353128</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>5.356107552</v>
+        <v>5.165353128</v>
       </c>
       <c r="Q24">
-        <v>9.746107552</v>
+        <v>9.555353128</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.118263897504924</v>
+        <v>0.1192049870829101</v>
       </c>
       <c r="T24">
-        <v>1.327201731072345</v>
+        <v>1.344438117190168</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.053840364104242</v>
+        <v>3.656190798634622</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1058868400538407</v>
+        <v>0.1060418400538408</v>
       </c>
       <c r="C25">
-        <v>103.9040787044007</v>
+        <v>102.4274699144112</v>
       </c>
       <c r="D25">
-        <v>37.82751870440074</v>
+        <v>37.73018991441121</v>
       </c>
       <c r="E25">
-        <v>30.79544</v>
+        <v>32.17472000000001</v>
       </c>
       <c r="F25">
-        <v>31.72344</v>
+        <v>33.10272000000001</v>
       </c>
       <c r="G25">
         <v>97.8</v>
@@ -3337,28 +3337,28 @@
         <v>7.11</v>
       </c>
       <c r="M25">
-        <v>1.944646872</v>
+        <v>2.029196736</v>
       </c>
       <c r="N25">
-        <v>5.165353128</v>
+        <v>5.080803264</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>5.165353128</v>
+        <v>5.080803264</v>
       </c>
       <c r="Q25">
-        <v>9.555353128</v>
+        <v>9.470803264000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1192049870829101</v>
+        <v>0.1201708421761063</v>
       </c>
       <c r="T25">
-        <v>1.344438117190168</v>
+        <v>1.362128092416354</v>
       </c>
       <c r="U25">
         <v>0.0613</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.656190798634622</v>
+        <v>3.503849515358179</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1060418400538408</v>
+        <v>0.1068968400538407</v>
       </c>
       <c r="C26">
-        <v>102.4274699144112</v>
+        <v>100.52018695471</v>
       </c>
       <c r="D26">
-        <v>37.73018991441121</v>
+        <v>37.20218695470998</v>
       </c>
       <c r="E26">
-        <v>32.17472</v>
+        <v>33.554</v>
       </c>
       <c r="F26">
-        <v>33.10272</v>
+        <v>34.482</v>
       </c>
       <c r="G26">
         <v>97.8</v>
@@ -3419,45 +3419,45 @@
         <v>7.11</v>
       </c>
       <c r="M26">
-        <v>2.029196736</v>
+        <v>2.2102962</v>
       </c>
       <c r="N26">
-        <v>5.080803264</v>
+        <v>4.8997038</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>5.080803264</v>
+        <v>4.8997038</v>
       </c>
       <c r="Q26">
-        <v>9.470803264000001</v>
+        <v>9.2897038</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1201708421761063</v>
+        <v>0.121162453405121</v>
       </c>
       <c r="T26">
-        <v>1.362128092416354</v>
+        <v>1.380289800315239</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.50384951535818</v>
+        <v>3.216763436502311</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1068968400538407</v>
+        <v>0.1070798400538407</v>
       </c>
       <c r="C27">
-        <v>100.52018695471</v>
+        <v>99.02981005552209</v>
       </c>
       <c r="D27">
-        <v>37.20218695470998</v>
+        <v>37.09109005552209</v>
       </c>
       <c r="E27">
-        <v>33.554</v>
+        <v>34.93328</v>
       </c>
       <c r="F27">
-        <v>34.482</v>
+        <v>35.86128</v>
       </c>
       <c r="G27">
         <v>97.8</v>
@@ -3501,28 +3501,28 @@
         <v>7.11</v>
       </c>
       <c r="M27">
-        <v>2.2102962</v>
+        <v>2.298708048</v>
       </c>
       <c r="N27">
-        <v>4.8997038</v>
+        <v>4.811291951999999</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>4.8997038</v>
+        <v>4.811291951999999</v>
       </c>
       <c r="Q27">
-        <v>9.2897038</v>
+        <v>9.201291951999998</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.121162453405121</v>
+        <v>0.1221808649376226</v>
       </c>
       <c r="T27">
-        <v>1.380289800315239</v>
+        <v>1.398942365184364</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.216763436502311</v>
+        <v>3.093041765867607</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1070798400538407</v>
+        <v>0.1093688400538408</v>
       </c>
       <c r="C28">
-        <v>99.02981005552209</v>
+        <v>96.31494637859511</v>
       </c>
       <c r="D28">
-        <v>37.09109005552209</v>
+        <v>35.75550637859512</v>
       </c>
       <c r="E28">
-        <v>34.93328</v>
+        <v>36.31256</v>
       </c>
       <c r="F28">
-        <v>35.86128</v>
+        <v>37.24056</v>
       </c>
       <c r="G28">
         <v>97.8</v>
@@ -3583,45 +3583,45 @@
         <v>7.11</v>
       </c>
       <c r="M28">
-        <v>2.298708048</v>
+        <v>2.677596264</v>
       </c>
       <c r="N28">
-        <v>4.811291951999999</v>
+        <v>4.432403735999999</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>4.811291951999999</v>
+        <v>4.432403735999999</v>
       </c>
       <c r="Q28">
-        <v>9.201291951999998</v>
+        <v>8.822403735999998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1221808649376226</v>
+        <v>0.1232271781559462</v>
       </c>
       <c r="T28">
-        <v>1.398942365184364</v>
+        <v>1.418105959227985</v>
       </c>
       <c r="U28">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.093041765867607</v>
+        <v>2.655366716630584</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1093688400538408</v>
+        <v>0.1096298400538407</v>
       </c>
       <c r="C29">
-        <v>96.31494637859511</v>
+        <v>94.78946223399845</v>
       </c>
       <c r="D29">
-        <v>35.75550637859512</v>
+        <v>35.60930223399847</v>
       </c>
       <c r="E29">
-        <v>36.31256</v>
+        <v>37.69184000000001</v>
       </c>
       <c r="F29">
-        <v>37.24056</v>
+        <v>38.61984</v>
       </c>
       <c r="G29">
         <v>97.8</v>
@@ -3665,28 +3665,28 @@
         <v>7.11</v>
       </c>
       <c r="M29">
-        <v>2.677596264</v>
+        <v>2.776766496</v>
       </c>
       <c r="N29">
-        <v>4.432403735999999</v>
+        <v>4.333233504</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>4.432403735999999</v>
+        <v>4.333233504</v>
       </c>
       <c r="Q29">
-        <v>8.822403735999998</v>
+        <v>8.723233504</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1232271781559462</v>
+        <v>0.1243025556303344</v>
       </c>
       <c r="T29">
-        <v>1.418105959227985</v>
+        <v>1.437801875328374</v>
       </c>
       <c r="U29">
         <v>0.07190000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.655366716630584</v>
+        <v>2.560532191036635</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1096298400538407</v>
+        <v>0.1110218400538407</v>
       </c>
       <c r="C30">
-        <v>94.78946223399845</v>
+        <v>92.65018912940639</v>
       </c>
       <c r="D30">
-        <v>35.60930223399847</v>
+        <v>34.8493091294064</v>
       </c>
       <c r="E30">
-        <v>37.69184000000001</v>
+        <v>39.07112000000001</v>
       </c>
       <c r="F30">
-        <v>38.61984</v>
+        <v>39.99912</v>
       </c>
       <c r="G30">
         <v>97.8</v>
@@ -3747,45 +3747,45 @@
         <v>7.11</v>
       </c>
       <c r="M30">
-        <v>2.776766496</v>
+        <v>3.031933296</v>
       </c>
       <c r="N30">
-        <v>4.333233504</v>
+        <v>4.078066703999999</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>4.333233504</v>
+        <v>4.078066703999999</v>
       </c>
       <c r="Q30">
-        <v>8.723233504</v>
+        <v>8.468066703999998</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1243025556303344</v>
+        <v>0.1254082254279447</v>
       </c>
       <c r="T30">
-        <v>1.437801875328374</v>
+        <v>1.458052605966802</v>
       </c>
       <c r="U30">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.560532191036635</v>
+        <v>2.345038398232623</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1110218400538407</v>
+        <v>0.1113218400538407</v>
       </c>
       <c r="C31">
-        <v>92.65018912940639</v>
+        <v>91.11134717677763</v>
       </c>
       <c r="D31">
-        <v>34.8493091294064</v>
+        <v>34.68974717677762</v>
       </c>
       <c r="E31">
-        <v>39.07112</v>
+        <v>40.4504</v>
       </c>
       <c r="F31">
-        <v>39.99912</v>
+        <v>41.3784</v>
       </c>
       <c r="G31">
         <v>97.8</v>
@@ -3829,28 +3829,28 @@
         <v>7.11</v>
       </c>
       <c r="M31">
-        <v>3.031933296</v>
+        <v>3.13648272</v>
       </c>
       <c r="N31">
-        <v>4.078066704</v>
+        <v>3.97351728</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>4.078066704</v>
+        <v>3.97351728</v>
       </c>
       <c r="Q31">
-        <v>8.468066704</v>
+        <v>8.36351728</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1254082254279447</v>
+        <v>0.1265454857912011</v>
       </c>
       <c r="T31">
-        <v>1.458052605966801</v>
+        <v>1.478881928909184</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.345038398232624</v>
+        <v>2.26687045162487</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1113218400538407</v>
+        <v>0.1116218400538408</v>
       </c>
       <c r="C32">
-        <v>91.11134717677763</v>
+        <v>89.57395971359335</v>
       </c>
       <c r="D32">
-        <v>34.68974717677762</v>
+        <v>34.53163971359334</v>
       </c>
       <c r="E32">
-        <v>40.4504</v>
+        <v>41.82968</v>
       </c>
       <c r="F32">
-        <v>41.3784</v>
+        <v>42.75768</v>
       </c>
       <c r="G32">
         <v>97.8</v>
@@ -3911,28 +3911,28 @@
         <v>7.11</v>
       </c>
       <c r="M32">
-        <v>3.13648272</v>
+        <v>3.241032144000001</v>
       </c>
       <c r="N32">
-        <v>3.97351728</v>
+        <v>3.868967856</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>3.97351728</v>
+        <v>3.868967856</v>
       </c>
       <c r="Q32">
-        <v>8.36351728</v>
+        <v>8.258967856</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1265454857912011</v>
+        <v>0.1277157102229576</v>
       </c>
       <c r="T32">
-        <v>1.478881928909184</v>
+        <v>1.500315000342651</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.26687045162487</v>
+        <v>2.193745598346648</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1116218400538408</v>
+        <v>0.1119218400538407</v>
       </c>
       <c r="C33">
-        <v>89.57395971359335</v>
+        <v>88.03800694245386</v>
       </c>
       <c r="D33">
-        <v>34.53163971359334</v>
+        <v>34.37496694245386</v>
       </c>
       <c r="E33">
-        <v>41.82968</v>
+        <v>43.20896</v>
       </c>
       <c r="F33">
-        <v>42.75768</v>
+        <v>44.13696</v>
       </c>
       <c r="G33">
         <v>97.8</v>
@@ -3993,28 +3993,28 @@
         <v>7.11</v>
       </c>
       <c r="M33">
-        <v>3.241032144000001</v>
+        <v>3.345581568000001</v>
       </c>
       <c r="N33">
-        <v>3.868967856</v>
+        <v>3.764418432</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>3.868967856</v>
+        <v>3.764418432</v>
       </c>
       <c r="Q33">
-        <v>8.258967856</v>
+        <v>8.154418432</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1277157102229576</v>
+        <v>0.128920353020354</v>
       </c>
       <c r="T33">
-        <v>1.500315000342651</v>
+        <v>1.522378456230043</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.193745598346648</v>
+        <v>2.125191048398315</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1119218400538407</v>
+        <v>0.1122218400538408</v>
       </c>
       <c r="C34">
-        <v>88.03800694245386</v>
+        <v>86.50346942362603</v>
       </c>
       <c r="D34">
-        <v>34.37496694245386</v>
+        <v>34.21970942362604</v>
       </c>
       <c r="E34">
-        <v>43.20896</v>
+        <v>44.58824000000001</v>
       </c>
       <c r="F34">
-        <v>44.13696</v>
+        <v>45.51624</v>
       </c>
       <c r="G34">
         <v>97.8</v>
@@ -4075,28 +4075,28 @@
         <v>7.11</v>
       </c>
       <c r="M34">
-        <v>3.345581568000001</v>
+        <v>3.450130992000001</v>
       </c>
       <c r="N34">
-        <v>3.764418432</v>
+        <v>3.659869008</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>3.764418432</v>
+        <v>3.659869008</v>
       </c>
       <c r="Q34">
-        <v>8.154418432</v>
+        <v>8.049869008</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.128920353020354</v>
+        <v>0.1301609553042399</v>
       </c>
       <c r="T34">
-        <v>1.522378456230043</v>
+        <v>1.545100522740939</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.125191048398315</v>
+        <v>2.060791319658972</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1122218400538408</v>
+        <v>0.1125218400538407</v>
       </c>
       <c r="C35">
-        <v>86.50346942362603</v>
+        <v>84.97032806700273</v>
       </c>
       <c r="D35">
-        <v>34.21970942362604</v>
+        <v>34.06584806700274</v>
       </c>
       <c r="E35">
-        <v>44.58824000000001</v>
+        <v>45.96752000000001</v>
       </c>
       <c r="F35">
-        <v>45.51624</v>
+        <v>46.89552</v>
       </c>
       <c r="G35">
         <v>97.8</v>
@@ -4157,28 +4157,28 @@
         <v>7.11</v>
       </c>
       <c r="M35">
-        <v>3.450130992000001</v>
+        <v>3.554680416000001</v>
       </c>
       <c r="N35">
-        <v>3.659869008</v>
+        <v>3.555319584</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>3.659869008</v>
+        <v>3.555319584</v>
       </c>
       <c r="Q35">
-        <v>8.049869008</v>
+        <v>7.945319584</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1301609553042399</v>
+        <v>0.1314391515967284</v>
       </c>
       <c r="T35">
-        <v>1.545100522740939</v>
+        <v>1.568511136721862</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.060791319658972</v>
+        <v>2.000179810257238</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1125218400538407</v>
+        <v>0.1177918400538407</v>
       </c>
       <c r="C36">
-        <v>84.97032806700273</v>
+        <v>81.09733462421755</v>
       </c>
       <c r="D36">
-        <v>34.06584806700274</v>
+        <v>31.57213462421754</v>
       </c>
       <c r="E36">
-        <v>45.96752000000001</v>
+        <v>47.34680000000001</v>
       </c>
       <c r="F36">
-        <v>46.89552</v>
+        <v>48.27480000000001</v>
       </c>
       <c r="G36">
         <v>97.8</v>
@@ -4239,45 +4239,45 @@
         <v>7.11</v>
       </c>
       <c r="M36">
-        <v>3.554680416000001</v>
+        <v>4.344732</v>
       </c>
       <c r="N36">
-        <v>3.555319584</v>
+        <v>2.765268</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>3.555319584</v>
+        <v>2.765268</v>
       </c>
       <c r="Q36">
-        <v>7.945319584</v>
+        <v>7.155268</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1314391515967284</v>
+        <v>0.1327566770059088</v>
       </c>
       <c r="T36">
-        <v>1.568511136721862</v>
+        <v>1.592642077286814</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.000179810257238</v>
+        <v>1.636464573649192</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1177918400538407</v>
+        <v>0.1182338400538407</v>
       </c>
       <c r="C37">
-        <v>81.09733462421755</v>
+        <v>79.52539766314062</v>
       </c>
       <c r="D37">
-        <v>31.57213462421754</v>
+        <v>31.37947766314062</v>
       </c>
       <c r="E37">
-        <v>47.34680000000001</v>
+        <v>48.72608000000001</v>
       </c>
       <c r="F37">
-        <v>48.27480000000001</v>
+        <v>49.65408000000001</v>
       </c>
       <c r="G37">
         <v>97.8</v>
@@ -4321,28 +4321,28 @@
         <v>7.11</v>
       </c>
       <c r="M37">
-        <v>4.344732</v>
+        <v>4.468867200000001</v>
       </c>
       <c r="N37">
-        <v>2.765268</v>
+        <v>2.641132799999999</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>2.765268</v>
+        <v>2.641132799999999</v>
       </c>
       <c r="Q37">
-        <v>7.155268</v>
+        <v>7.031132799999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1327566770059088</v>
+        <v>0.1341153750841262</v>
       </c>
       <c r="T37">
-        <v>1.592642077286814</v>
+        <v>1.61752710974442</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.636464573649192</v>
+        <v>1.591007224381158</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1182338400538407</v>
+        <v>0.1186758400538407</v>
       </c>
       <c r="C38">
-        <v>79.52539766314064</v>
+        <v>77.95579767345869</v>
       </c>
       <c r="D38">
-        <v>31.37947766314062</v>
+        <v>31.18915767345871</v>
       </c>
       <c r="E38">
-        <v>48.72608</v>
+        <v>50.10536</v>
       </c>
       <c r="F38">
-        <v>49.65408</v>
+        <v>51.03336</v>
       </c>
       <c r="G38">
         <v>97.8</v>
@@ -4403,28 +4403,28 @@
         <v>7.11</v>
       </c>
       <c r="M38">
-        <v>4.4688672</v>
+        <v>4.5930024</v>
       </c>
       <c r="N38">
-        <v>2.6411328</v>
+        <v>2.516997600000001</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>2.6411328</v>
+        <v>2.516997600000001</v>
       </c>
       <c r="Q38">
-        <v>7.0311328</v>
+        <v>6.9069976</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1341153750841262</v>
+        <v>0.1355172064346679</v>
       </c>
       <c r="T38">
-        <v>1.61752710974442</v>
+        <v>1.643202143232427</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.591007224381159</v>
+        <v>1.548007029127614</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1186758400538407</v>
+        <v>0.1191178400538407</v>
       </c>
       <c r="C39">
-        <v>77.95579767345869</v>
+        <v>76.38849238955039</v>
       </c>
       <c r="D39">
-        <v>31.18915767345871</v>
+        <v>31.00113238955038</v>
       </c>
       <c r="E39">
-        <v>50.10536</v>
+        <v>51.48464</v>
       </c>
       <c r="F39">
-        <v>51.03336</v>
+        <v>52.41264</v>
       </c>
       <c r="G39">
         <v>97.8</v>
@@ -4485,28 +4485,28 @@
         <v>7.11</v>
       </c>
       <c r="M39">
-        <v>4.5930024</v>
+        <v>4.717137599999999</v>
       </c>
       <c r="N39">
-        <v>2.516997600000001</v>
+        <v>2.392862400000001</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>2.516997600000001</v>
+        <v>2.392862400000001</v>
       </c>
       <c r="Q39">
-        <v>6.9069976</v>
+        <v>6.782862400000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1355172064346679</v>
+        <v>0.136964258151356</v>
       </c>
       <c r="T39">
-        <v>1.643202143232427</v>
+        <v>1.669705403607143</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.548007029127614</v>
+        <v>1.507270002045308</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1191178400538407</v>
+        <v>0.1417118400538407</v>
       </c>
       <c r="C40">
-        <v>76.38849238955039</v>
+        <v>67.70626016992551</v>
       </c>
       <c r="D40">
-        <v>31.00113238955038</v>
+        <v>23.69818016992551</v>
       </c>
       <c r="E40">
-        <v>51.48464</v>
+        <v>52.86392</v>
       </c>
       <c r="F40">
-        <v>52.41264</v>
+        <v>53.79192</v>
       </c>
       <c r="G40">
         <v>97.8</v>
@@ -4567,45 +4567,45 @@
         <v>7.11</v>
       </c>
       <c r="M40">
-        <v>4.717137599999999</v>
+        <v>7.896653856</v>
       </c>
       <c r="N40">
-        <v>2.392862400000001</v>
+        <v>-0.786653856</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P40">
-        <v>2.392862400000001</v>
+        <v>-0.786653856</v>
       </c>
       <c r="Q40">
-        <v>6.782862400000001</v>
+        <v>3.603346144</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.136964258151356</v>
+        <v>0.1384587541866242</v>
       </c>
       <c r="T40">
-        <v>1.669705403607143</v>
+        <v>1.697077623338408</v>
       </c>
       <c r="U40">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y40">
-        <v>1.507270002045308</v>
+        <v>0.9003813678115968</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1417118400538407</v>
+        <v>0.1427218400538408</v>
       </c>
       <c r="C41">
-        <v>67.70626016992551</v>
+        <v>66.0800269346348</v>
       </c>
       <c r="D41">
-        <v>23.69818016992551</v>
+        <v>23.4512269346348</v>
       </c>
       <c r="E41">
-        <v>52.86392</v>
+        <v>54.2432</v>
       </c>
       <c r="F41">
-        <v>53.79192</v>
+        <v>55.1712</v>
       </c>
       <c r="G41">
         <v>97.8</v>
@@ -4649,28 +4649,28 @@
         <v>7.11</v>
       </c>
       <c r="M41">
-        <v>7.896653856</v>
+        <v>8.09913216</v>
       </c>
       <c r="N41">
-        <v>-0.786653856</v>
+        <v>-0.9891321599999996</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>-0.786653856</v>
+        <v>-0.9891321599999996</v>
       </c>
       <c r="Q41">
-        <v>3.603346144</v>
+        <v>3.40086784</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1384587541866242</v>
+        <v>0.1400030667564013</v>
       </c>
       <c r="T41">
-        <v>1.697077623338408</v>
+        <v>1.725362250394048</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.9003813678115968</v>
+        <v>0.8778718336163069</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1427218400538408</v>
+        <v>0.1437318400538407</v>
       </c>
       <c r="C42">
-        <v>66.0800269346348</v>
+        <v>64.45888750269765</v>
       </c>
       <c r="D42">
-        <v>23.4512269346348</v>
+        <v>23.20936750269766</v>
       </c>
       <c r="E42">
-        <v>54.2432</v>
+        <v>55.62248</v>
       </c>
       <c r="F42">
-        <v>55.1712</v>
+        <v>56.55048</v>
       </c>
       <c r="G42">
         <v>97.8</v>
@@ -4731,28 +4731,28 @@
         <v>7.11</v>
       </c>
       <c r="M42">
-        <v>8.09913216</v>
+        <v>8.301610464000001</v>
       </c>
       <c r="N42">
-        <v>-0.9891321599999996</v>
+        <v>-1.191610464000001</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-0.9891321599999996</v>
+        <v>-1.191610464000001</v>
       </c>
       <c r="Q42">
-        <v>3.40086784</v>
+        <v>3.198389535999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1400030667564013</v>
+        <v>0.1415997289048148</v>
       </c>
       <c r="T42">
-        <v>1.725362250394048</v>
+        <v>1.754605678366829</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8778718336163069</v>
+        <v>0.8564603254793237</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1437318400538407</v>
+        <v>0.1447418400538407</v>
       </c>
       <c r="C43">
-        <v>64.45888750269765</v>
+        <v>62.84268588121812</v>
       </c>
       <c r="D43">
-        <v>23.20936750269766</v>
+        <v>22.97244588121812</v>
       </c>
       <c r="E43">
-        <v>55.62248</v>
+        <v>57.00176</v>
       </c>
       <c r="F43">
-        <v>56.55048</v>
+        <v>57.92976</v>
       </c>
       <c r="G43">
         <v>97.8</v>
@@ -4813,28 +4813,28 @@
         <v>7.11</v>
       </c>
       <c r="M43">
-        <v>8.301610464000001</v>
+        <v>8.504088768000001</v>
       </c>
       <c r="N43">
-        <v>-1.191610464000001</v>
+        <v>-1.394088768</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-1.191610464000001</v>
+        <v>-1.394088768</v>
       </c>
       <c r="Q43">
-        <v>3.198389535999999</v>
+        <v>2.995911231999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1415997289048148</v>
+        <v>0.1432514483686909</v>
       </c>
       <c r="T43">
-        <v>1.754605678366829</v>
+        <v>1.784857500407636</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.8564603254793237</v>
+        <v>0.8360684129679112</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1447418400538408</v>
+        <v>0.1457518400538407</v>
       </c>
       <c r="C44">
-        <v>62.84268588121812</v>
+        <v>61.2312723824498</v>
       </c>
       <c r="D44">
-        <v>22.97244588121812</v>
+        <v>22.7403123824498</v>
       </c>
       <c r="E44">
-        <v>57.00176</v>
+        <v>58.38104</v>
       </c>
       <c r="F44">
-        <v>57.92975999999999</v>
+        <v>59.30904</v>
       </c>
       <c r="G44">
         <v>97.8</v>
@@ -4895,28 +4895,28 @@
         <v>7.11</v>
       </c>
       <c r="M44">
-        <v>8.504088768000001</v>
+        <v>8.706567072</v>
       </c>
       <c r="N44">
-        <v>-1.394088768</v>
+        <v>-1.596567072</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-1.394088768</v>
+        <v>-1.596567072</v>
       </c>
       <c r="Q44">
-        <v>2.995911231999999</v>
+        <v>2.793432928</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1432514483686909</v>
+        <v>0.144961122901475</v>
       </c>
       <c r="T44">
-        <v>1.784857500407636</v>
+        <v>1.816170789888472</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8360684129679112</v>
+        <v>0.8166249615035412</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1457518400538407</v>
+        <v>0.1705218400538407</v>
       </c>
       <c r="C45">
-        <v>61.2312723824498</v>
+        <v>55.33572211679206</v>
       </c>
       <c r="D45">
-        <v>22.7403123824498</v>
+        <v>18.22404211679206</v>
       </c>
       <c r="E45">
-        <v>58.38104</v>
+        <v>59.76032</v>
       </c>
       <c r="F45">
-        <v>59.30904</v>
+        <v>60.68832</v>
       </c>
       <c r="G45">
         <v>97.8</v>
@@ -4977,45 +4977,45 @@
         <v>7.11</v>
       </c>
       <c r="M45">
-        <v>8.706567072</v>
+        <v>12.186214656</v>
       </c>
       <c r="N45">
-        <v>-1.596567072</v>
+        <v>-5.076214656</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-1.596567072</v>
+        <v>-5.076214656</v>
       </c>
       <c r="Q45">
-        <v>2.793432928</v>
+        <v>-0.6862146560000006</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.144961122901475</v>
+        <v>0.1467318572390013</v>
       </c>
       <c r="T45">
-        <v>1.816170789888472</v>
+        <v>1.84860241113648</v>
       </c>
       <c r="U45">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.8166249615035412</v>
+        <v>0.5834461480209789</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1705218400538407</v>
+        <v>0.1720718400538408</v>
       </c>
       <c r="C46">
-        <v>55.33572211679206</v>
+        <v>53.73274010002423</v>
       </c>
       <c r="D46">
-        <v>18.22404211679206</v>
+        <v>18.00034010002424</v>
       </c>
       <c r="E46">
-        <v>59.76032</v>
+        <v>61.1396</v>
       </c>
       <c r="F46">
-        <v>60.68832</v>
+        <v>62.0676</v>
       </c>
       <c r="G46">
         <v>97.8</v>
@@ -5059,28 +5059,28 @@
         <v>7.11</v>
       </c>
       <c r="M46">
-        <v>12.186214656</v>
+        <v>12.46317408</v>
       </c>
       <c r="N46">
-        <v>-5.076214656</v>
+        <v>-5.35317408</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-5.076214656</v>
+        <v>-5.35317408</v>
       </c>
       <c r="Q46">
-        <v>-0.6862146560000006</v>
+        <v>-0.9631740799999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1467318572390013</v>
+        <v>0.1485669819160741</v>
       </c>
       <c r="T46">
-        <v>1.84860241113648</v>
+        <v>1.882213364066235</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5834461480209789</v>
+        <v>0.5704806780649573</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1720718400538408</v>
+        <v>0.1736218400538408</v>
       </c>
       <c r="C47">
-        <v>53.73274010002423</v>
+        <v>52.13518341786033</v>
       </c>
       <c r="D47">
-        <v>18.00034010002424</v>
+        <v>17.78206341786033</v>
       </c>
       <c r="E47">
-        <v>61.1396</v>
+        <v>62.51888</v>
       </c>
       <c r="F47">
-        <v>62.0676</v>
+        <v>63.44688</v>
       </c>
       <c r="G47">
         <v>97.8</v>
@@ -5141,28 +5141,28 @@
         <v>7.11</v>
       </c>
       <c r="M47">
-        <v>12.46317408</v>
+        <v>12.740133504</v>
       </c>
       <c r="N47">
-        <v>-5.35317408</v>
+        <v>-5.630133504000001</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-5.35317408</v>
+        <v>-5.630133504000001</v>
       </c>
       <c r="Q47">
-        <v>-0.9631740799999999</v>
+        <v>-1.240133504000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1485669819160741</v>
+        <v>0.1504700741737792</v>
       </c>
       <c r="T47">
-        <v>1.882213364066235</v>
+        <v>1.917069167104498</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5704806780649573</v>
+        <v>0.5580789241939799</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1736218400538408</v>
+        <v>0.1751718400538408</v>
       </c>
       <c r="C48">
-        <v>52.13518341786033</v>
+        <v>50.54285706800387</v>
       </c>
       <c r="D48">
-        <v>17.78206341786033</v>
+        <v>17.56901706800387</v>
       </c>
       <c r="E48">
-        <v>62.51888</v>
+        <v>63.89816</v>
       </c>
       <c r="F48">
-        <v>63.44688</v>
+        <v>64.82616</v>
       </c>
       <c r="G48">
         <v>97.8</v>
@@ -5223,28 +5223,28 @@
         <v>7.11</v>
       </c>
       <c r="M48">
-        <v>12.740133504</v>
+        <v>13.017092928</v>
       </c>
       <c r="N48">
-        <v>-5.630133504000001</v>
+        <v>-5.907092928</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-5.630133504000001</v>
+        <v>-5.907092928</v>
       </c>
       <c r="Q48">
-        <v>-1.240133504000001</v>
+        <v>-1.517092928</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1504700741737792</v>
+        <v>0.1524449812336618</v>
       </c>
       <c r="T48">
-        <v>1.917069167104498</v>
+        <v>1.95324028346496</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5580789241939799</v>
+        <v>0.5462049045302783</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1751718400538408</v>
+        <v>0.1767218400538408</v>
       </c>
       <c r="C49">
-        <v>50.54285706800387</v>
+        <v>48.95557528278448</v>
       </c>
       <c r="D49">
-        <v>17.56901706800387</v>
+        <v>17.36101528278449</v>
       </c>
       <c r="E49">
-        <v>63.89816</v>
+        <v>65.27744000000001</v>
       </c>
       <c r="F49">
-        <v>64.82616</v>
+        <v>66.20544000000001</v>
       </c>
       <c r="G49">
         <v>97.8</v>
@@ -5305,28 +5305,28 @@
         <v>7.11</v>
       </c>
       <c r="M49">
-        <v>13.017092928</v>
+        <v>13.294052352</v>
       </c>
       <c r="N49">
-        <v>-5.907092928</v>
+        <v>-6.184052352000003</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-5.907092928</v>
+        <v>-6.184052352000003</v>
       </c>
       <c r="Q49">
-        <v>-1.517092928</v>
+        <v>-1.794052352000003</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1524449812336618</v>
+        <v>0.154495846257386</v>
       </c>
       <c r="T49">
-        <v>1.95324028346496</v>
+        <v>1.990802596608517</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5462049045302783</v>
+        <v>0.5348256356858974</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1767218400538407</v>
+        <v>0.1782718400538408</v>
       </c>
       <c r="C50">
-        <v>48.95557528278449</v>
+        <v>47.37316098890453</v>
       </c>
       <c r="D50">
-        <v>17.3610152827845</v>
+        <v>17.15788098890453</v>
       </c>
       <c r="E50">
-        <v>65.27744</v>
+        <v>66.65672000000001</v>
       </c>
       <c r="F50">
-        <v>66.20544</v>
+        <v>67.58472</v>
       </c>
       <c r="G50">
         <v>97.8</v>
@@ -5387,28 +5387,28 @@
         <v>7.11</v>
       </c>
       <c r="M50">
-        <v>13.294052352</v>
+        <v>13.571011776</v>
       </c>
       <c r="N50">
-        <v>-6.184052351999999</v>
+        <v>-6.461011776</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-6.184052351999999</v>
+        <v>-6.461011776</v>
       </c>
       <c r="Q50">
-        <v>-1.794052352</v>
+        <v>-2.071011776000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.154495846257386</v>
+        <v>0.156627137360472</v>
       </c>
       <c r="T50">
-        <v>1.990802596608517</v>
+        <v>2.029837941640057</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5348256356858975</v>
+        <v>0.5239108267943485</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1782718400538408</v>
+        <v>0.1798218400538407</v>
       </c>
       <c r="C51">
-        <v>47.37316098890453</v>
+        <v>45.79544530467487</v>
       </c>
       <c r="D51">
-        <v>17.15788098890453</v>
+        <v>16.95944530467487</v>
       </c>
       <c r="E51">
-        <v>66.65672000000001</v>
+        <v>68.036</v>
       </c>
       <c r="F51">
-        <v>67.58472</v>
+        <v>68.964</v>
       </c>
       <c r="G51">
         <v>97.8</v>
@@ -5469,28 +5469,28 @@
         <v>7.11</v>
       </c>
       <c r="M51">
-        <v>13.571011776</v>
+        <v>13.8479712</v>
       </c>
       <c r="N51">
-        <v>-6.461011776</v>
+        <v>-6.7379712</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-6.461011776</v>
+        <v>-6.7379712</v>
       </c>
       <c r="Q51">
-        <v>-2.071011776000001</v>
+        <v>-2.3479712</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.156627137360472</v>
+        <v>0.1588436801076815</v>
       </c>
       <c r="T51">
-        <v>2.029837941640057</v>
+        <v>2.070434700472858</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5239108267943485</v>
+        <v>0.5134326102584615</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1798218400538407</v>
+        <v>0.1813718400538407</v>
       </c>
       <c r="C52">
-        <v>45.79544530467487</v>
+        <v>44.22226707173944</v>
       </c>
       <c r="D52">
-        <v>16.95944530467487</v>
+        <v>16.76554707173943</v>
       </c>
       <c r="E52">
-        <v>68.036</v>
+        <v>69.41528</v>
       </c>
       <c r="F52">
-        <v>68.964</v>
+        <v>70.34327999999999</v>
       </c>
       <c r="G52">
         <v>97.8</v>
@@ -5551,28 +5551,28 @@
         <v>7.11</v>
       </c>
       <c r="M52">
-        <v>13.8479712</v>
+        <v>14.124930624</v>
       </c>
       <c r="N52">
-        <v>-6.7379712</v>
+        <v>-7.014930623999999</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-6.7379712</v>
+        <v>-7.014930623999999</v>
       </c>
       <c r="Q52">
-        <v>-2.3479712</v>
+        <v>-2.624930623999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1588436801076815</v>
+        <v>0.1611506939874301</v>
       </c>
       <c r="T52">
-        <v>2.070434700472858</v>
+        <v>2.112688469870263</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5134326102584615</v>
+        <v>0.5033653041749624</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1813718400538407</v>
+        <v>0.2011218400538408</v>
       </c>
       <c r="C53">
-        <v>44.22226707173944</v>
+        <v>40.71115838266341</v>
       </c>
       <c r="D53">
-        <v>16.76554707173943</v>
+        <v>14.63371838266341</v>
       </c>
       <c r="E53">
-        <v>69.41528</v>
+        <v>70.79456</v>
       </c>
       <c r="F53">
-        <v>70.34327999999999</v>
+        <v>71.72256</v>
       </c>
       <c r="G53">
         <v>97.8</v>
@@ -5633,45 +5633,45 @@
         <v>7.11</v>
       </c>
       <c r="M53">
-        <v>14.124930624</v>
+        <v>16.912179648</v>
       </c>
       <c r="N53">
-        <v>-7.014930623999999</v>
+        <v>-9.802179648000003</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-7.014930623999999</v>
+        <v>-9.802179648000003</v>
       </c>
       <c r="Q53">
-        <v>-2.624930623999999</v>
+        <v>-5.412179648000003</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1611506939874301</v>
+        <v>0.1635538334455016</v>
       </c>
       <c r="T53">
-        <v>2.112688469870263</v>
+        <v>2.156702812992561</v>
       </c>
       <c r="U53">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V53">
         <v>0</v>
       </c>
       <c r="W53">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.5033653041749624</v>
+        <v>0.4204070763191552</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2011218400538408</v>
+        <v>0.2030218400538408</v>
       </c>
       <c r="C54">
-        <v>40.71115838266341</v>
+        <v>39.15503231014868</v>
       </c>
       <c r="D54">
-        <v>14.63371838266341</v>
+        <v>14.45687231014869</v>
       </c>
       <c r="E54">
-        <v>70.79456</v>
+        <v>72.17384</v>
       </c>
       <c r="F54">
-        <v>71.72256</v>
+        <v>73.10184</v>
       </c>
       <c r="G54">
         <v>97.8</v>
@@ -5715,28 +5715,28 @@
         <v>7.11</v>
       </c>
       <c r="M54">
-        <v>16.912179648</v>
+        <v>17.237413872</v>
       </c>
       <c r="N54">
-        <v>-9.802179648000003</v>
+        <v>-10.127413872</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-9.802179648000003</v>
+        <v>-10.127413872</v>
       </c>
       <c r="Q54">
-        <v>-5.412179648000003</v>
+        <v>-5.737413872000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1635538334455016</v>
+        <v>0.166059234157108</v>
       </c>
       <c r="T54">
-        <v>2.156702812992561</v>
+        <v>2.202590106886019</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4204070763191552</v>
+        <v>0.4124748673320013</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2030218400538408</v>
+        <v>0.2049218400538407</v>
       </c>
       <c r="C55">
-        <v>39.15503231014868</v>
+        <v>37.60312951129222</v>
       </c>
       <c r="D55">
-        <v>14.45687231014869</v>
+        <v>14.28424951129224</v>
       </c>
       <c r="E55">
-        <v>72.17384</v>
+        <v>73.55312000000001</v>
       </c>
       <c r="F55">
-        <v>73.10184</v>
+        <v>74.48112</v>
       </c>
       <c r="G55">
         <v>97.8</v>
@@ -5797,28 +5797,28 @@
         <v>7.11</v>
       </c>
       <c r="M55">
-        <v>17.237413872</v>
+        <v>17.562648096</v>
       </c>
       <c r="N55">
-        <v>-10.127413872</v>
+        <v>-10.452648096</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-10.127413872</v>
+        <v>-10.452648096</v>
       </c>
       <c r="Q55">
-        <v>-5.737413872000002</v>
+        <v>-6.062648096000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.166059234157108</v>
+        <v>0.1686735653344364</v>
       </c>
       <c r="T55">
-        <v>2.202590106886019</v>
+        <v>2.250472500513976</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4124748673320013</v>
+        <v>0.4048364438628902</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2049218400538407</v>
+        <v>0.2068218400538407</v>
       </c>
       <c r="C56">
-        <v>37.60312951129222</v>
+        <v>36.05530048674761</v>
       </c>
       <c r="D56">
-        <v>14.28424951129224</v>
+        <v>14.11570048674762</v>
       </c>
       <c r="E56">
-        <v>73.55312000000001</v>
+        <v>74.9324</v>
       </c>
       <c r="F56">
-        <v>74.48112</v>
+        <v>75.8604</v>
       </c>
       <c r="G56">
         <v>97.8</v>
@@ -5879,28 +5879,28 @@
         <v>7.11</v>
       </c>
       <c r="M56">
-        <v>17.562648096</v>
+        <v>17.88788232</v>
       </c>
       <c r="N56">
-        <v>-10.452648096</v>
+        <v>-10.77788232</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-10.452648096</v>
+        <v>-10.77788232</v>
       </c>
       <c r="Q56">
-        <v>-6.062648096000001</v>
+        <v>-6.38788232</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1686735653344364</v>
+        <v>0.171404089008535</v>
       </c>
       <c r="T56">
-        <v>2.250472500513976</v>
+        <v>2.300483000525398</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4048364438628902</v>
+        <v>0.3974757812472013</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2068218400538407</v>
+        <v>0.2087218400538408</v>
       </c>
       <c r="C57">
-        <v>36.05530048674761</v>
+        <v>34.51140271103407</v>
       </c>
       <c r="D57">
-        <v>14.11570048674762</v>
+        <v>13.95108271103407</v>
       </c>
       <c r="E57">
-        <v>74.9324</v>
+        <v>76.31168000000001</v>
       </c>
       <c r="F57">
-        <v>75.8604</v>
+        <v>77.23968000000001</v>
       </c>
       <c r="G57">
         <v>97.8</v>
@@ -5961,28 +5961,28 @@
         <v>7.11</v>
       </c>
       <c r="M57">
-        <v>17.88788232</v>
+        <v>18.213116544</v>
       </c>
       <c r="N57">
-        <v>-10.77788232</v>
+        <v>-11.103116544</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-10.77788232</v>
+        <v>-11.103116544</v>
       </c>
       <c r="Q57">
-        <v>-6.38788232</v>
+        <v>-6.713116544000003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.171404089008535</v>
+        <v>0.1742587273950926</v>
       </c>
       <c r="T57">
-        <v>2.300483000525398</v>
+        <v>2.352766705082793</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3974757812472013</v>
+        <v>0.3903779994392155</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2087218400538408</v>
+        <v>0.2106218400538408</v>
       </c>
       <c r="C58">
-        <v>34.51140271103407</v>
+        <v>32.97130023057694</v>
       </c>
       <c r="D58">
-        <v>13.95108271103407</v>
+        <v>13.79026023057695</v>
       </c>
       <c r="E58">
-        <v>76.31168000000001</v>
+        <v>77.69096</v>
       </c>
       <c r="F58">
-        <v>77.23968000000001</v>
+        <v>78.61896</v>
       </c>
       <c r="G58">
         <v>97.8</v>
@@ -6043,28 +6043,28 @@
         <v>7.11</v>
       </c>
       <c r="M58">
-        <v>18.213116544</v>
+        <v>18.538350768</v>
       </c>
       <c r="N58">
-        <v>-11.103116544</v>
+        <v>-11.428350768</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-11.103116544</v>
+        <v>-11.428350768</v>
       </c>
       <c r="Q58">
-        <v>-6.713116544000003</v>
+        <v>-7.038350768000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1742587273950926</v>
+        <v>0.1772461396600948</v>
       </c>
       <c r="T58">
-        <v>2.352766705082793</v>
+        <v>2.407482209852161</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3903779994392155</v>
+        <v>0.3835292626069486</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2106218400538408</v>
+        <v>0.2125218400538408</v>
       </c>
       <c r="C59">
-        <v>32.97130023057694</v>
+        <v>31.43486328923299</v>
       </c>
       <c r="D59">
-        <v>13.79026023057695</v>
+        <v>13.63310328923301</v>
       </c>
       <c r="E59">
-        <v>77.69096</v>
+        <v>79.07024000000001</v>
       </c>
       <c r="F59">
-        <v>78.61896</v>
+        <v>79.99824000000001</v>
       </c>
       <c r="G59">
         <v>97.8</v>
@@ -6125,28 +6125,28 @@
         <v>7.11</v>
       </c>
       <c r="M59">
-        <v>18.538350768</v>
+        <v>18.863584992</v>
       </c>
       <c r="N59">
-        <v>-11.428350768</v>
+        <v>-11.753584992</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-11.428350768</v>
+        <v>-11.753584992</v>
       </c>
       <c r="Q59">
-        <v>-7.038350768000002</v>
+        <v>-7.363584992000004</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1772461396600948</v>
+        <v>0.1803758096520018</v>
       </c>
       <c r="T59">
-        <v>2.407482209852161</v>
+        <v>2.464803214848641</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3835292626069486</v>
+        <v>0.3769166891137253</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2125218400538407</v>
+        <v>0.2144218400538407</v>
       </c>
       <c r="C60">
-        <v>31.43486328923301</v>
+        <v>29.90196797913279</v>
       </c>
       <c r="D60">
-        <v>13.63310328923301</v>
+        <v>13.47948797913278</v>
       </c>
       <c r="E60">
-        <v>79.07024</v>
+        <v>80.44951999999999</v>
       </c>
       <c r="F60">
-        <v>79.99824</v>
+        <v>81.37751999999999</v>
       </c>
       <c r="G60">
         <v>97.8</v>
@@ -6207,28 +6207,28 @@
         <v>7.11</v>
       </c>
       <c r="M60">
-        <v>18.863584992</v>
+        <v>19.188819216</v>
       </c>
       <c r="N60">
-        <v>-11.753584992</v>
+        <v>-12.078819216</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-11.753584992</v>
+        <v>-12.078819216</v>
       </c>
       <c r="Q60">
-        <v>-7.363584992000001</v>
+        <v>-7.688819216</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1803758096520018</v>
+        <v>0.1836581464727823</v>
       </c>
       <c r="T60">
-        <v>2.46480321484864</v>
+        <v>2.524920366430314</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3769166891137253</v>
+        <v>0.3705282706541707</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2144218400538407</v>
+        <v>0.2163218400538408</v>
       </c>
       <c r="C61">
-        <v>29.90196797913279</v>
+        <v>28.37249591486542</v>
       </c>
       <c r="D61">
-        <v>13.47948797913278</v>
+        <v>13.32929591486543</v>
       </c>
       <c r="E61">
-        <v>80.44951999999999</v>
+        <v>81.8288</v>
       </c>
       <c r="F61">
-        <v>81.37751999999999</v>
+        <v>82.7568</v>
       </c>
       <c r="G61">
         <v>97.8</v>
@@ -6289,28 +6289,28 @@
         <v>7.11</v>
       </c>
       <c r="M61">
-        <v>19.188819216</v>
+        <v>19.51405344</v>
       </c>
       <c r="N61">
-        <v>-12.078819216</v>
+        <v>-12.40405344</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-12.078819216</v>
+        <v>-12.40405344</v>
       </c>
       <c r="Q61">
-        <v>-7.688819216</v>
+        <v>-8.014053440000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1836581464727823</v>
+        <v>0.1871046001346019</v>
       </c>
       <c r="T61">
-        <v>2.524920366430314</v>
+        <v>2.588043375591073</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3705282706541707</v>
+        <v>0.3643527994766012</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2163218400538408</v>
+        <v>0.2182218400538407</v>
       </c>
       <c r="C62">
-        <v>28.37249591486542</v>
+        <v>26.84633392920553</v>
       </c>
       <c r="D62">
-        <v>13.32929591486543</v>
+        <v>13.18241392920552</v>
       </c>
       <c r="E62">
-        <v>81.8288</v>
+        <v>83.20808</v>
       </c>
       <c r="F62">
-        <v>82.7568</v>
+        <v>84.13607999999999</v>
       </c>
       <c r="G62">
         <v>97.8</v>
@@ -6371,28 +6371,28 @@
         <v>7.11</v>
       </c>
       <c r="M62">
-        <v>19.51405344</v>
+        <v>19.839287664</v>
       </c>
       <c r="N62">
-        <v>-12.40405344</v>
+        <v>-12.729287664</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-12.40405344</v>
+        <v>-12.729287664</v>
       </c>
       <c r="Q62">
-        <v>-8.014053440000001</v>
+        <v>-8.339287664</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1871046001346019</v>
+        <v>0.1907277950098481</v>
       </c>
       <c r="T62">
-        <v>2.588043375591073</v>
+        <v>2.654403462144689</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3643527994766012</v>
+        <v>0.35837980276387</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2182218400538407</v>
+        <v>0.2201218400538408</v>
       </c>
       <c r="C63">
-        <v>26.84633392920553</v>
+        <v>25.32337378873801</v>
       </c>
       <c r="D63">
-        <v>13.18241392920552</v>
+        <v>13.03873378873801</v>
       </c>
       <c r="E63">
-        <v>83.20808</v>
+        <v>84.58736</v>
       </c>
       <c r="F63">
-        <v>84.13607999999999</v>
+        <v>85.51536</v>
       </c>
       <c r="G63">
         <v>97.8</v>
@@ -6453,28 +6453,28 @@
         <v>7.11</v>
       </c>
       <c r="M63">
-        <v>19.839287664</v>
+        <v>20.164521888</v>
       </c>
       <c r="N63">
-        <v>-12.729287664</v>
+        <v>-13.054521888</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-12.729287664</v>
+        <v>-13.054521888</v>
       </c>
       <c r="Q63">
-        <v>-8.339287664</v>
+        <v>-8.664521887999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1907277950098481</v>
+        <v>0.1945416843522125</v>
       </c>
       <c r="T63">
-        <v>2.654403462144689</v>
+        <v>2.724256184832708</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.35837980276387</v>
+        <v>0.3525994833644528</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2201218400538408</v>
+        <v>0.2220218400538408</v>
       </c>
       <c r="C64">
-        <v>25.32337378873801</v>
+        <v>23.80351192787994</v>
       </c>
       <c r="D64">
-        <v>13.03873378873801</v>
+        <v>12.89815192787994</v>
       </c>
       <c r="E64">
-        <v>84.58736</v>
+        <v>85.96664</v>
       </c>
       <c r="F64">
-        <v>85.51536</v>
+        <v>86.89464</v>
       </c>
       <c r="G64">
         <v>97.8</v>
@@ -6535,28 +6535,28 @@
         <v>7.11</v>
       </c>
       <c r="M64">
-        <v>20.164521888</v>
+        <v>20.489756112</v>
       </c>
       <c r="N64">
-        <v>-13.054521888</v>
+        <v>-13.379756112</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-13.054521888</v>
+        <v>-13.379756112</v>
       </c>
       <c r="Q64">
-        <v>-8.664521887999999</v>
+        <v>-8.989756111999998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1945416843522125</v>
+        <v>0.1985617298752453</v>
       </c>
       <c r="T64">
-        <v>2.724256184832708</v>
+        <v>2.797884730368727</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3525994833644528</v>
+        <v>0.3470026661681916</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2220218400538408</v>
+        <v>0.2239218400538407</v>
       </c>
       <c r="C65">
-        <v>23.80351192787994</v>
+        <v>22.28664919992494</v>
       </c>
       <c r="D65">
-        <v>12.89815192787994</v>
+        <v>12.76056919992494</v>
       </c>
       <c r="E65">
-        <v>85.96664</v>
+        <v>87.34592000000001</v>
       </c>
       <c r="F65">
-        <v>86.89464</v>
+        <v>88.27392</v>
       </c>
       <c r="G65">
         <v>97.8</v>
@@ -6617,28 +6617,28 @@
         <v>7.11</v>
       </c>
       <c r="M65">
-        <v>20.489756112</v>
+        <v>20.814990336</v>
       </c>
       <c r="N65">
-        <v>-13.379756112</v>
+        <v>-13.704990336</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-13.379756112</v>
+        <v>-13.704990336</v>
       </c>
       <c r="Q65">
-        <v>-8.989756111999998</v>
+        <v>-9.314990336000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1985617298752453</v>
+        <v>0.2028051112606687</v>
       </c>
       <c r="T65">
-        <v>2.797884730368727</v>
+        <v>2.875603750656747</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3470026661681916</v>
+        <v>0.3415807495093136</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2239218400538407</v>
+        <v>0.2258218400538408</v>
       </c>
       <c r="C66">
-        <v>22.28664919992494</v>
+        <v>20.77269064385304</v>
       </c>
       <c r="D66">
-        <v>12.76056919992494</v>
+        <v>12.62589064385304</v>
       </c>
       <c r="E66">
-        <v>87.34592000000001</v>
+        <v>88.7252</v>
       </c>
       <c r="F66">
-        <v>88.27392</v>
+        <v>89.6532</v>
       </c>
       <c r="G66">
         <v>97.8</v>
@@ -6699,28 +6699,28 @@
         <v>7.11</v>
       </c>
       <c r="M66">
-        <v>20.814990336</v>
+        <v>21.14022456</v>
       </c>
       <c r="N66">
-        <v>-13.704990336</v>
+        <v>-14.03022456</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-13.704990336</v>
+        <v>-14.03022456</v>
       </c>
       <c r="Q66">
-        <v>-9.314990336000001</v>
+        <v>-9.64022456</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2028051112606687</v>
+        <v>0.2072909715824022</v>
       </c>
       <c r="T66">
-        <v>2.875603750656747</v>
+        <v>2.957763857818369</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3415807495093136</v>
+        <v>0.3363256610553241</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2258218400538408</v>
+        <v>0.2277218400538408</v>
       </c>
       <c r="C67">
-        <v>20.77269064385304</v>
+        <v>19.26154526575317</v>
       </c>
       <c r="D67">
-        <v>12.62589064385304</v>
+        <v>12.49402526575319</v>
       </c>
       <c r="E67">
-        <v>88.7252</v>
+        <v>90.10448000000001</v>
       </c>
       <c r="F67">
-        <v>89.6532</v>
+        <v>91.03248000000001</v>
       </c>
       <c r="G67">
         <v>97.8</v>
@@ -6781,28 +6781,28 @@
         <v>7.11</v>
       </c>
       <c r="M67">
-        <v>21.14022456</v>
+        <v>21.465458784</v>
       </c>
       <c r="N67">
-        <v>-14.03022456</v>
+        <v>-14.355458784</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-14.03022456</v>
+        <v>-14.355458784</v>
       </c>
       <c r="Q67">
-        <v>-9.64022456</v>
+        <v>-9.965458784000003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2072909715824022</v>
+        <v>0.2120407060407081</v>
       </c>
       <c r="T67">
-        <v>2.957763857818369</v>
+        <v>3.044756912460086</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3363256610553241</v>
+        <v>0.331229817706001</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2277218400538408</v>
+        <v>0.2296218400538408</v>
       </c>
       <c r="C68">
-        <v>19.26154526575317</v>
+        <v>17.75312583380115</v>
       </c>
       <c r="D68">
-        <v>12.49402526575319</v>
+        <v>12.36488583380115</v>
       </c>
       <c r="E68">
-        <v>90.10448000000001</v>
+        <v>91.48376</v>
       </c>
       <c r="F68">
-        <v>91.03248000000001</v>
+        <v>92.41176</v>
       </c>
       <c r="G68">
         <v>97.8</v>
@@ -6863,28 +6863,28 @@
         <v>7.11</v>
       </c>
       <c r="M68">
-        <v>21.465458784</v>
+        <v>21.790693008</v>
       </c>
       <c r="N68">
-        <v>-14.355458784</v>
+        <v>-14.680693008</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-14.355458784</v>
+        <v>-14.680693008</v>
       </c>
       <c r="Q68">
-        <v>-9.965458784000003</v>
+        <v>-10.290693008</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2120407060407081</v>
+        <v>0.2170783031934568</v>
       </c>
       <c r="T68">
-        <v>3.044756912460086</v>
+        <v>3.137022273443725</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.331229817706001</v>
+        <v>0.3262860890835234</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2296218400538408</v>
+        <v>0.2315218400538407</v>
       </c>
       <c r="C69">
-        <v>17.75312583380115</v>
+        <v>16.24734868582215</v>
       </c>
       <c r="D69">
-        <v>12.36488583380115</v>
+        <v>12.23838868582215</v>
       </c>
       <c r="E69">
-        <v>91.48376</v>
+        <v>92.86304000000001</v>
       </c>
       <c r="F69">
-        <v>92.41176</v>
+        <v>93.79104000000001</v>
       </c>
       <c r="G69">
         <v>97.8</v>
@@ -6945,28 +6945,28 @@
         <v>7.11</v>
       </c>
       <c r="M69">
-        <v>21.790693008</v>
+        <v>22.115927232</v>
       </c>
       <c r="N69">
-        <v>-14.680693008</v>
+        <v>-15.005927232</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-14.680693008</v>
+        <v>-15.005927232</v>
       </c>
       <c r="Q69">
-        <v>-10.290693008</v>
+        <v>-10.615927232</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2170783031934568</v>
+        <v>0.2224307501682524</v>
       </c>
       <c r="T69">
-        <v>3.137022273443725</v>
+        <v>3.235054219488841</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3262860890835234</v>
+        <v>0.3214877642440598</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2315218400538407</v>
+        <v>0.2334218400538408</v>
       </c>
       <c r="C70">
-        <v>16.24734868582215</v>
+        <v>14.74413354854607</v>
       </c>
       <c r="D70">
-        <v>12.23838868582215</v>
+        <v>12.11445354854608</v>
       </c>
       <c r="E70">
-        <v>92.86304000000001</v>
+        <v>94.24232000000001</v>
       </c>
       <c r="F70">
-        <v>93.79104000000001</v>
+        <v>95.17032</v>
       </c>
       <c r="G70">
         <v>97.8</v>
@@ -7027,28 +7027,28 @@
         <v>7.11</v>
       </c>
       <c r="M70">
-        <v>22.115927232</v>
+        <v>22.441161456</v>
       </c>
       <c r="N70">
-        <v>-15.005927232</v>
+        <v>-15.331161456</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-15.005927232</v>
+        <v>-15.331161456</v>
       </c>
       <c r="Q70">
-        <v>-10.615927232</v>
+        <v>-10.941161456</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2224307501682524</v>
+        <v>0.2281285163027121</v>
       </c>
       <c r="T70">
-        <v>3.235054219488841</v>
+        <v>3.339410807214288</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3214877642440598</v>
+        <v>0.316828521284001</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2334218400538408</v>
+        <v>0.2353218400538408</v>
       </c>
       <c r="C71">
-        <v>14.74413354854607</v>
+        <v>13.24340336773471</v>
       </c>
       <c r="D71">
-        <v>12.11445354854608</v>
+        <v>11.99300336773473</v>
       </c>
       <c r="E71">
-        <v>94.24232000000001</v>
+        <v>95.62160000000002</v>
       </c>
       <c r="F71">
-        <v>95.17032</v>
+        <v>96.54960000000001</v>
       </c>
       <c r="G71">
         <v>97.8</v>
@@ -7109,28 +7109,28 @@
         <v>7.11</v>
       </c>
       <c r="M71">
-        <v>22.441161456</v>
+        <v>22.76639568</v>
       </c>
       <c r="N71">
-        <v>-15.331161456</v>
+        <v>-15.65639568</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-15.331161456</v>
+        <v>-15.65639568</v>
       </c>
       <c r="Q71">
-        <v>-10.941161456</v>
+        <v>-11.26639568</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2281285163027121</v>
+        <v>0.2342061335128025</v>
       </c>
       <c r="T71">
-        <v>3.339410807214288</v>
+        <v>3.450724500788097</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.316828521284001</v>
+        <v>0.3123023995513724</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2353218400538408</v>
+        <v>0.2372218400538408</v>
       </c>
       <c r="C72">
-        <v>13.24340336773471</v>
+        <v>11.74508414842576</v>
       </c>
       <c r="D72">
-        <v>11.99300336773473</v>
+        <v>11.87396414842576</v>
       </c>
       <c r="E72">
-        <v>95.62160000000002</v>
+        <v>97.00088000000001</v>
       </c>
       <c r="F72">
-        <v>96.54960000000001</v>
+        <v>97.92888000000001</v>
       </c>
       <c r="G72">
         <v>97.8</v>
@@ -7191,28 +7191,28 @@
         <v>7.11</v>
       </c>
       <c r="M72">
-        <v>22.76639568</v>
+        <v>23.091629904</v>
       </c>
       <c r="N72">
-        <v>-15.65639568</v>
+        <v>-15.981629904</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-15.65639568</v>
+        <v>-15.981629904</v>
       </c>
       <c r="Q72">
-        <v>-11.26639568</v>
+        <v>-11.591629904</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2342061335128025</v>
+        <v>0.240702896737382</v>
       </c>
       <c r="T72">
-        <v>3.450724500788097</v>
+        <v>3.569715000815274</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3123023995513724</v>
+        <v>0.3079037742055785</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2372218400538408</v>
+        <v>0.2391218400538408</v>
       </c>
       <c r="C73">
-        <v>11.74508414842578</v>
+        <v>10.24910480459722</v>
       </c>
       <c r="D73">
-        <v>11.87396414842576</v>
+        <v>11.75726480459723</v>
       </c>
       <c r="E73">
-        <v>97.00088</v>
+        <v>98.38016</v>
       </c>
       <c r="F73">
-        <v>97.92887999999999</v>
+        <v>99.30816</v>
       </c>
       <c r="G73">
         <v>97.8</v>
@@ -7273,28 +7273,28 @@
         <v>7.11</v>
       </c>
       <c r="M73">
-        <v>23.091629904</v>
+        <v>23.416864128</v>
       </c>
       <c r="N73">
-        <v>-15.981629904</v>
+        <v>-16.306864128</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-15.981629904</v>
+        <v>-16.306864128</v>
       </c>
       <c r="Q73">
-        <v>-11.591629904</v>
+        <v>-11.916864128</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2407028967373819</v>
+        <v>0.2476637144780027</v>
       </c>
       <c r="T73">
-        <v>3.569715000815272</v>
+        <v>3.697204822272961</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3079037742055785</v>
+        <v>0.3036273328971676</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2391218400538408</v>
+        <v>0.2410218400538408</v>
       </c>
       <c r="C74">
-        <v>10.24910480459722</v>
+        <v>8.755397017611031</v>
       </c>
       <c r="D74">
-        <v>11.75726480459723</v>
+        <v>11.64283701761103</v>
       </c>
       <c r="E74">
-        <v>98.38016</v>
+        <v>99.75944</v>
       </c>
       <c r="F74">
-        <v>99.30816</v>
+        <v>100.68744</v>
       </c>
       <c r="G74">
         <v>97.8</v>
@@ -7355,28 +7355,28 @@
         <v>7.11</v>
       </c>
       <c r="M74">
-        <v>23.416864128</v>
+        <v>23.742098352</v>
       </c>
       <c r="N74">
-        <v>-16.306864128</v>
+        <v>-16.632098352</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-16.306864128</v>
+        <v>-16.632098352</v>
       </c>
       <c r="Q74">
-        <v>-11.916864128</v>
+        <v>-12.242098352</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2476637144780027</v>
+        <v>0.2551401483475583</v>
       </c>
       <c r="T74">
-        <v>3.697204822272961</v>
+        <v>3.834138334208996</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3036273328971676</v>
+        <v>0.2994680543643298</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2410218400538408</v>
+        <v>0.2429218400538408</v>
       </c>
       <c r="C75">
-        <v>8.755397017611031</v>
+        <v>7.263895102842881</v>
       </c>
       <c r="D75">
-        <v>11.64283701761103</v>
+        <v>11.53061510284289</v>
       </c>
       <c r="E75">
-        <v>99.75944</v>
+        <v>101.13872</v>
       </c>
       <c r="F75">
-        <v>100.68744</v>
+        <v>102.06672</v>
       </c>
       <c r="G75">
         <v>97.8</v>
@@ -7437,28 +7437,28 @@
         <v>7.11</v>
       </c>
       <c r="M75">
-        <v>23.742098352</v>
+        <v>24.067332576</v>
       </c>
       <c r="N75">
-        <v>-16.632098352</v>
+        <v>-16.957332576</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-16.632098352</v>
+        <v>-16.957332576</v>
       </c>
       <c r="Q75">
-        <v>-12.242098352</v>
+        <v>-12.567332576</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2551401483475583</v>
+        <v>0.2631916925147721</v>
       </c>
       <c r="T75">
-        <v>3.834138334208996</v>
+        <v>3.981605193217034</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2994680543643298</v>
+        <v>0.2954211887648117</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2429218400538408</v>
+        <v>0.2448218400538408</v>
       </c>
       <c r="C76">
-        <v>7.263895102842881</v>
+        <v>5.774535883951756</v>
       </c>
       <c r="D76">
-        <v>11.53061510284289</v>
+        <v>11.42053588395176</v>
       </c>
       <c r="E76">
-        <v>101.13872</v>
+        <v>102.518</v>
       </c>
       <c r="F76">
-        <v>102.06672</v>
+        <v>103.446</v>
       </c>
       <c r="G76">
         <v>97.8</v>
@@ -7519,28 +7519,28 @@
         <v>7.11</v>
       </c>
       <c r="M76">
-        <v>24.067332576</v>
+        <v>24.3925668</v>
       </c>
       <c r="N76">
-        <v>-16.957332576</v>
+        <v>-17.2825668</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-16.957332576</v>
+        <v>-17.2825668</v>
       </c>
       <c r="Q76">
-        <v>-12.567332576</v>
+        <v>-12.8925668</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2631916925147721</v>
+        <v>0.271887360215363</v>
       </c>
       <c r="T76">
-        <v>3.981605193217034</v>
+        <v>4.140869400945716</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2954211887648117</v>
+        <v>0.2914822395812809</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2448218400538408</v>
+        <v>0.2467218400538407</v>
       </c>
       <c r="C77">
-        <v>5.774535883951756</v>
+        <v>4.28725857428303</v>
       </c>
       <c r="D77">
-        <v>11.42053588395176</v>
+        <v>11.31253857428302</v>
       </c>
       <c r="E77">
-        <v>102.518</v>
+        <v>103.89728</v>
       </c>
       <c r="F77">
-        <v>103.446</v>
+        <v>104.82528</v>
       </c>
       <c r="G77">
         <v>97.8</v>
@@ -7601,28 +7601,28 @@
         <v>7.11</v>
       </c>
       <c r="M77">
-        <v>24.3925668</v>
+        <v>24.717801024</v>
       </c>
       <c r="N77">
-        <v>-17.2825668</v>
+        <v>-17.607801024</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-17.2825668</v>
+        <v>-17.607801024</v>
       </c>
       <c r="Q77">
-        <v>-12.8925668</v>
+        <v>-13.217801024</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.271887360215363</v>
+        <v>0.2813076668910031</v>
       </c>
       <c r="T77">
-        <v>4.140869400945716</v>
+        <v>4.313405625985121</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2914822395812809</v>
+        <v>0.2876469469552114</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2467218400538407</v>
+        <v>0.2486218400538407</v>
       </c>
       <c r="C78">
-        <v>4.28725857428303</v>
+        <v>2.802004664937598</v>
       </c>
       <c r="D78">
-        <v>11.31253857428302</v>
+        <v>11.2065646649376</v>
       </c>
       <c r="E78">
-        <v>103.89728</v>
+        <v>105.27656</v>
       </c>
       <c r="F78">
-        <v>104.82528</v>
+        <v>106.20456</v>
       </c>
       <c r="G78">
         <v>97.8</v>
@@ -7683,28 +7683,28 @@
         <v>7.11</v>
       </c>
       <c r="M78">
-        <v>24.717801024</v>
+        <v>25.043035248</v>
       </c>
       <c r="N78">
-        <v>-17.607801024</v>
+        <v>-17.933035248</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-17.607801024</v>
+        <v>-17.933035248</v>
       </c>
       <c r="Q78">
-        <v>-13.217801024</v>
+        <v>-13.543035248</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2813076668910031</v>
+        <v>0.2915471306688728</v>
       </c>
       <c r="T78">
-        <v>4.313405625985121</v>
+        <v>4.500945001027952</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2876469469552114</v>
+        <v>0.2839112723194295</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2486218400538407</v>
+        <v>0.2505218400538408</v>
       </c>
       <c r="C79">
-        <v>2.802004664937598</v>
+        <v>1.318717819074052</v>
       </c>
       <c r="D79">
-        <v>11.2065646649376</v>
+        <v>11.10255781907405</v>
       </c>
       <c r="E79">
-        <v>105.27656</v>
+        <v>106.65584</v>
       </c>
       <c r="F79">
-        <v>106.20456</v>
+        <v>107.58384</v>
       </c>
       <c r="G79">
         <v>97.8</v>
@@ -7765,28 +7765,28 @@
         <v>7.11</v>
       </c>
       <c r="M79">
-        <v>25.043035248</v>
+        <v>25.368269472</v>
       </c>
       <c r="N79">
-        <v>-17.933035248</v>
+        <v>-18.258269472</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-17.933035248</v>
+        <v>-18.258269472</v>
       </c>
       <c r="Q79">
-        <v>-13.543035248</v>
+        <v>-13.868269472</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2915471306688728</v>
+        <v>0.3027174547901852</v>
       </c>
       <c r="T79">
-        <v>4.500945001027952</v>
+        <v>4.705533410165587</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2839112723194295</v>
+        <v>0.2802713842127701</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2505218400538408</v>
+        <v>0.2524218400538407</v>
       </c>
       <c r="C80">
-        <v>1.318717819074052</v>
+        <v>-0.1626562279576973</v>
       </c>
       <c r="D80">
-        <v>11.10255781907405</v>
+        <v>11.00046377204231</v>
       </c>
       <c r="E80">
-        <v>106.65584</v>
+        <v>108.03512</v>
       </c>
       <c r="F80">
-        <v>107.58384</v>
+        <v>108.96312</v>
       </c>
       <c r="G80">
         <v>97.8</v>
@@ -7847,28 +7847,28 @@
         <v>7.11</v>
       </c>
       <c r="M80">
-        <v>25.368269472</v>
+        <v>25.693503696</v>
       </c>
       <c r="N80">
-        <v>-18.258269472</v>
+        <v>-18.583503696</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-18.258269472</v>
+        <v>-18.583503696</v>
       </c>
       <c r="Q80">
-        <v>-13.868269472</v>
+        <v>-14.193503696</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3027174547901852</v>
+        <v>0.3149516193040036</v>
       </c>
       <c r="T80">
-        <v>4.705533410165587</v>
+        <v>4.929606429697282</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2802713842127701</v>
+        <v>0.2767236451721021</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2524218400538407</v>
+        <v>0.2543218400538408</v>
       </c>
       <c r="C81">
-        <v>-0.1626562279576973</v>
+        <v>-1.642169763022821</v>
       </c>
       <c r="D81">
-        <v>11.00046377204231</v>
+        <v>10.90023023697719</v>
       </c>
       <c r="E81">
-        <v>108.03512</v>
+        <v>109.4144</v>
       </c>
       <c r="F81">
-        <v>108.96312</v>
+        <v>110.3424</v>
       </c>
       <c r="G81">
         <v>97.8</v>
@@ -7929,28 +7929,28 @@
         <v>7.11</v>
       </c>
       <c r="M81">
-        <v>25.693503696</v>
+        <v>26.01873792</v>
       </c>
       <c r="N81">
-        <v>-18.583503696</v>
+        <v>-18.90873792</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-18.583503696</v>
+        <v>-18.90873792</v>
       </c>
       <c r="Q81">
-        <v>-14.193503696</v>
+        <v>-14.51873792</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3149516193040036</v>
+        <v>0.3284092002692038</v>
       </c>
       <c r="T81">
-        <v>4.929606429697282</v>
+        <v>5.176086751182146</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2767236451721021</v>
+        <v>0.2732645996074509</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2543218400538408</v>
+        <v>0.2562218400538407</v>
       </c>
       <c r="C82">
-        <v>-1.642169763022821</v>
+        <v>-3.1198731844935</v>
       </c>
       <c r="D82">
-        <v>10.90023023697719</v>
+        <v>10.8018068155065</v>
       </c>
       <c r="E82">
-        <v>109.4144</v>
+        <v>110.79368</v>
       </c>
       <c r="F82">
-        <v>110.3424</v>
+        <v>111.72168</v>
       </c>
       <c r="G82">
         <v>97.8</v>
@@ -8011,28 +8011,28 @@
         <v>7.11</v>
       </c>
       <c r="M82">
-        <v>26.01873792</v>
+        <v>26.343972144</v>
       </c>
       <c r="N82">
-        <v>-18.90873792</v>
+        <v>-19.233972144</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-18.90873792</v>
+        <v>-19.233972144</v>
       </c>
       <c r="Q82">
-        <v>-14.51873792</v>
+        <v>-14.843972144</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3284092002692038</v>
+        <v>0.3432833687044251</v>
       </c>
       <c r="T82">
-        <v>5.176086751182146</v>
+        <v>5.448512369665417</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2732645996074509</v>
+        <v>0.2698909625752601</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2562218400538407</v>
+        <v>0.2581218400538408</v>
       </c>
       <c r="C83">
-        <v>-3.1198731844935</v>
+        <v>-4.595815086746498</v>
       </c>
       <c r="D83">
-        <v>10.8018068155065</v>
+        <v>10.7051449132535</v>
       </c>
       <c r="E83">
-        <v>110.79368</v>
+        <v>112.17296</v>
       </c>
       <c r="F83">
-        <v>111.72168</v>
+        <v>113.10096</v>
       </c>
       <c r="G83">
         <v>97.8</v>
@@ -8093,28 +8093,28 @@
         <v>7.11</v>
       </c>
       <c r="M83">
-        <v>26.343972144</v>
+        <v>26.669206368</v>
       </c>
       <c r="N83">
-        <v>-19.233972144</v>
+        <v>-19.559206368</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-19.233972144</v>
+        <v>-19.559206368</v>
       </c>
       <c r="Q83">
-        <v>-14.843972144</v>
+        <v>-15.169206368</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3432833687044251</v>
+        <v>0.3598102225213376</v>
       </c>
       <c r="T83">
-        <v>5.448512369665417</v>
+        <v>5.751207501313496</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2698909625752601</v>
+        <v>0.2665996093731228</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2581218400538408</v>
+        <v>0.2600218400538408</v>
       </c>
       <c r="C84">
-        <v>-4.595815086746498</v>
+        <v>-6.070042340164136</v>
       </c>
       <c r="D84">
-        <v>10.7051449132535</v>
+        <v>10.61019765983587</v>
       </c>
       <c r="E84">
-        <v>112.17296</v>
+        <v>113.55224</v>
       </c>
       <c r="F84">
-        <v>113.10096</v>
+        <v>114.48024</v>
       </c>
       <c r="G84">
         <v>97.8</v>
@@ -8175,28 +8175,28 @@
         <v>7.11</v>
       </c>
       <c r="M84">
-        <v>26.669206368</v>
+        <v>26.994440592</v>
       </c>
       <c r="N84">
-        <v>-19.559206368</v>
+        <v>-19.884440592</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-19.559206368</v>
+        <v>-19.884440592</v>
       </c>
       <c r="Q84">
-        <v>-15.169206368</v>
+        <v>-15.494440592</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3598102225213376</v>
+        <v>0.3782814120814163</v>
       </c>
       <c r="T84">
-        <v>5.751207501313496</v>
+        <v>6.089513824920173</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2665996093731228</v>
+        <v>0.2633875658866996</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2600218400538408</v>
+        <v>0.2619218400538408</v>
       </c>
       <c r="C85">
-        <v>-6.070042340164136</v>
+        <v>-7.542600166915307</v>
       </c>
       <c r="D85">
-        <v>10.61019765983587</v>
+        <v>10.5169198330847</v>
       </c>
       <c r="E85">
-        <v>113.55224</v>
+        <v>114.93152</v>
       </c>
       <c r="F85">
-        <v>114.48024</v>
+        <v>115.85952</v>
       </c>
       <c r="G85">
         <v>97.8</v>
@@ -8257,28 +8257,28 @@
         <v>7.11</v>
       </c>
       <c r="M85">
-        <v>26.994440592</v>
+        <v>27.319674816</v>
       </c>
       <c r="N85">
-        <v>-19.884440592</v>
+        <v>-20.209674816</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-19.884440592</v>
+        <v>-20.209674816</v>
       </c>
       <c r="Q85">
-        <v>-15.494440592</v>
+        <v>-15.819674816</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3782814120814163</v>
+        <v>0.3990615003365049</v>
       </c>
       <c r="T85">
-        <v>6.089513824920173</v>
+        <v>6.470108438977685</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2633875658866996</v>
+        <v>0.2602519996261436</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2619218400538408</v>
+        <v>0.2638218400538407</v>
       </c>
       <c r="C86">
-        <v>-7.542600166915292</v>
+        <v>-9.013532212774223</v>
       </c>
       <c r="D86">
-        <v>10.5169198330847</v>
+        <v>10.42526778722578</v>
       </c>
       <c r="E86">
-        <v>114.93152</v>
+        <v>116.3108</v>
       </c>
       <c r="F86">
-        <v>115.85952</v>
+        <v>117.2388</v>
       </c>
       <c r="G86">
         <v>97.8</v>
@@ -8339,28 +8339,28 @@
         <v>7.11</v>
       </c>
       <c r="M86">
-        <v>27.319674816</v>
+        <v>27.64490904</v>
       </c>
       <c r="N86">
-        <v>-20.209674816</v>
+        <v>-20.53490904</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-20.209674816</v>
+        <v>-20.53490904</v>
       </c>
       <c r="Q86">
-        <v>-15.819674816</v>
+        <v>-16.14490904</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3990615003365046</v>
+        <v>0.4226122670256049</v>
       </c>
       <c r="T86">
-        <v>6.470108438977681</v>
+        <v>6.901449001576193</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2602519996261438</v>
+        <v>0.2571902113952479</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2638218400538407</v>
+        <v>0.2657218400538408</v>
       </c>
       <c r="C87">
-        <v>-9.013532212774223</v>
+        <v>-10.4828806152161</v>
       </c>
       <c r="D87">
-        <v>10.42526778722578</v>
+        <v>10.33519938478389</v>
       </c>
       <c r="E87">
-        <v>116.3108</v>
+        <v>117.69008</v>
       </c>
       <c r="F87">
-        <v>117.2388</v>
+        <v>118.61808</v>
       </c>
       <c r="G87">
         <v>97.8</v>
@@ -8421,28 +8421,28 @@
         <v>7.11</v>
       </c>
       <c r="M87">
-        <v>27.64490904</v>
+        <v>27.970143264</v>
       </c>
       <c r="N87">
-        <v>-20.53490904</v>
+        <v>-20.860143264</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-20.53490904</v>
+        <v>-20.860143264</v>
       </c>
       <c r="Q87">
-        <v>-16.14490904</v>
+        <v>-16.470143264</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4226122670256049</v>
+        <v>0.4495274289560053</v>
       </c>
       <c r="T87">
-        <v>6.901449001576193</v>
+        <v>7.394409644545921</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2571902113952479</v>
+        <v>0.2541996275418148</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2657218400538408</v>
+        <v>0.2676218400538407</v>
       </c>
       <c r="C88">
-        <v>-10.4828806152161</v>
+        <v>-11.95068606801338</v>
       </c>
       <c r="D88">
-        <v>10.33519938478389</v>
+        <v>10.24667393198663</v>
       </c>
       <c r="E88">
-        <v>117.69008</v>
+        <v>119.06936</v>
       </c>
       <c r="F88">
-        <v>118.61808</v>
+        <v>119.99736</v>
       </c>
       <c r="G88">
         <v>97.8</v>
@@ -8503,28 +8503,28 @@
         <v>7.11</v>
       </c>
       <c r="M88">
-        <v>27.970143264</v>
+        <v>28.295377488</v>
       </c>
       <c r="N88">
-        <v>-20.860143264</v>
+        <v>-21.185377488</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-20.860143264</v>
+        <v>-21.185377488</v>
       </c>
       <c r="Q88">
-        <v>-16.470143264</v>
+        <v>-16.795377488</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4495274289560053</v>
+        <v>0.4805833850295442</v>
       </c>
       <c r="T88">
-        <v>7.394409644545921</v>
+        <v>7.963210386434069</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2541996275418148</v>
+        <v>0.2512777927424835</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2676218400538407</v>
+        <v>0.2695218400538408</v>
       </c>
       <c r="C89">
-        <v>-11.95068606801338</v>
+        <v>-13.41698788254024</v>
       </c>
       <c r="D89">
-        <v>10.24667393198663</v>
+        <v>10.15965211745976</v>
       </c>
       <c r="E89">
-        <v>119.06936</v>
+        <v>120.44864</v>
       </c>
       <c r="F89">
-        <v>119.99736</v>
+        <v>121.37664</v>
       </c>
       <c r="G89">
         <v>97.8</v>
@@ -8585,28 +8585,28 @@
         <v>7.11</v>
       </c>
       <c r="M89">
-        <v>28.295377488</v>
+        <v>28.620611712</v>
       </c>
       <c r="N89">
-        <v>-21.185377488</v>
+        <v>-21.510611712</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-21.185377488</v>
+        <v>-21.510611712</v>
       </c>
       <c r="Q89">
-        <v>-16.795377488</v>
+        <v>-17.120611712</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4805833850295442</v>
+        <v>0.5168153337820062</v>
       </c>
       <c r="T89">
-        <v>7.963210386434069</v>
+        <v>8.626811251970242</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2512777927424835</v>
+        <v>0.2484223632795008</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2695218400538408</v>
+        <v>0.2714218400538407</v>
       </c>
       <c r="C90">
-        <v>-13.41698788254024</v>
+        <v>-14.88182404597978</v>
       </c>
       <c r="D90">
-        <v>10.15965211745976</v>
+        <v>10.07409595402023</v>
       </c>
       <c r="E90">
-        <v>120.44864</v>
+        <v>121.82792</v>
       </c>
       <c r="F90">
-        <v>121.37664</v>
+        <v>122.75592</v>
       </c>
       <c r="G90">
         <v>97.8</v>
@@ -8667,28 +8667,28 @@
         <v>7.11</v>
       </c>
       <c r="M90">
-        <v>28.620611712</v>
+        <v>28.945845936</v>
       </c>
       <c r="N90">
-        <v>-21.510611712</v>
+        <v>-21.835845936</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-21.510611712</v>
+        <v>-21.835845936</v>
       </c>
       <c r="Q90">
-        <v>-17.120611712</v>
+        <v>-17.445845936</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5168153337820062</v>
+        <v>0.5596349095803704</v>
       </c>
       <c r="T90">
-        <v>8.626811251970242</v>
+        <v>9.411066820331174</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2484223632795008</v>
+        <v>0.2456311007707423</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2714218400538407</v>
+        <v>0.2733218400538407</v>
       </c>
       <c r="C91">
-        <v>-14.88182404597978</v>
+        <v>-16.34523127661446</v>
       </c>
       <c r="D91">
-        <v>10.07409595402023</v>
+        <v>9.989968723385541</v>
       </c>
       <c r="E91">
-        <v>121.82792</v>
+        <v>123.2072</v>
       </c>
       <c r="F91">
-        <v>122.75592</v>
+        <v>124.1352</v>
       </c>
       <c r="G91">
         <v>97.8</v>
@@ -8749,28 +8749,28 @@
         <v>7.11</v>
       </c>
       <c r="M91">
-        <v>28.945845936</v>
+        <v>29.27108016</v>
       </c>
       <c r="N91">
-        <v>-21.835845936</v>
+        <v>-22.16108016</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-21.835845936</v>
+        <v>-22.16108016</v>
       </c>
       <c r="Q91">
-        <v>-17.445845936</v>
+        <v>-17.77108016</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5596349095803704</v>
+        <v>0.6110184005384076</v>
       </c>
       <c r="T91">
-        <v>9.411066820331174</v>
+        <v>10.35217350236429</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2456311007707423</v>
+        <v>0.2429018663177341</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2733218400538407</v>
+        <v>0.2752218400538408</v>
       </c>
       <c r="C92">
-        <v>-16.34523127661446</v>
+        <v>-17.80724507636944</v>
       </c>
       <c r="D92">
-        <v>9.989968723385541</v>
+        <v>9.907234923630563</v>
       </c>
       <c r="E92">
-        <v>123.2072</v>
+        <v>124.58648</v>
       </c>
       <c r="F92">
-        <v>124.1352</v>
+        <v>125.51448</v>
       </c>
       <c r="G92">
         <v>97.8</v>
@@ -8831,28 +8831,28 @@
         <v>7.11</v>
       </c>
       <c r="M92">
-        <v>29.27108016</v>
+        <v>29.596314384</v>
       </c>
       <c r="N92">
-        <v>-22.16108016</v>
+        <v>-22.486314384</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-22.16108016</v>
+        <v>-22.486314384</v>
       </c>
       <c r="Q92">
-        <v>-17.77108016</v>
+        <v>-18.096314384</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6110184005384076</v>
+        <v>0.6738204450426751</v>
       </c>
       <c r="T92">
-        <v>10.35217350236429</v>
+        <v>11.50241500262699</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2429018663177341</v>
+        <v>0.2402326150395172</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2752218400538408</v>
+        <v>0.2771218400538408</v>
       </c>
       <c r="C93">
-        <v>-17.80724507636944</v>
+        <v>-19.26789978076621</v>
       </c>
       <c r="D93">
-        <v>9.907234923630563</v>
+        <v>9.825860219233794</v>
       </c>
       <c r="E93">
-        <v>124.58648</v>
+        <v>125.96576</v>
       </c>
       <c r="F93">
-        <v>125.51448</v>
+        <v>126.89376</v>
       </c>
       <c r="G93">
         <v>97.8</v>
@@ -8913,28 +8913,28 @@
         <v>7.11</v>
       </c>
       <c r="M93">
-        <v>29.596314384</v>
+        <v>29.921548608</v>
       </c>
       <c r="N93">
-        <v>-22.486314384</v>
+        <v>-22.811548608</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-22.486314384</v>
+        <v>-22.811548608</v>
       </c>
       <c r="Q93">
-        <v>-18.096314384</v>
+        <v>-18.421548608</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6738204450426751</v>
+        <v>0.7523230006730097</v>
       </c>
       <c r="T93">
-        <v>11.50241500262699</v>
+        <v>12.94021687795537</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2402326150395172</v>
+        <v>0.2376213909630007</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2771218400538408</v>
+        <v>0.2790218400538408</v>
       </c>
       <c r="C94">
-        <v>-19.26789978076621</v>
+        <v>-20.72722860643466</v>
       </c>
       <c r="D94">
-        <v>9.825860219233794</v>
+        <v>9.745811393565347</v>
       </c>
       <c r="E94">
-        <v>125.96576</v>
+        <v>127.34504</v>
       </c>
       <c r="F94">
-        <v>126.89376</v>
+        <v>128.27304</v>
       </c>
       <c r="G94">
         <v>97.8</v>
@@ -8995,28 +8995,28 @@
         <v>7.11</v>
       </c>
       <c r="M94">
-        <v>29.921548608</v>
+        <v>30.246782832</v>
       </c>
       <c r="N94">
-        <v>-22.811548608</v>
+        <v>-23.13678283200001</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-22.811548608</v>
+        <v>-23.13678283200001</v>
       </c>
       <c r="Q94">
-        <v>-18.421548608</v>
+        <v>-18.746782832</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7523230006730097</v>
+        <v>0.8532548579120112</v>
       </c>
       <c r="T94">
-        <v>12.94021687795537</v>
+        <v>14.78881928909185</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2376213909630007</v>
+        <v>0.2350663222429684</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2790218400538408</v>
+        <v>0.2809218400538407</v>
       </c>
       <c r="C95">
-        <v>-20.72722860643466</v>
+        <v>-22.18526369632139</v>
       </c>
       <c r="D95">
-        <v>9.745811393565347</v>
+        <v>9.667056303678615</v>
       </c>
       <c r="E95">
-        <v>127.34504</v>
+        <v>128.72432</v>
       </c>
       <c r="F95">
-        <v>128.27304</v>
+        <v>129.65232</v>
       </c>
       <c r="G95">
         <v>97.8</v>
@@ -9077,28 +9077,28 @@
         <v>7.11</v>
       </c>
       <c r="M95">
-        <v>30.246782832</v>
+        <v>30.572017056</v>
       </c>
       <c r="N95">
-        <v>-23.13678283200001</v>
+        <v>-23.462017056</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-23.13678283200001</v>
+        <v>-23.462017056</v>
       </c>
       <c r="Q95">
-        <v>-18.746782832</v>
+        <v>-19.072017056</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8532548579120112</v>
+        <v>0.9878306675640132</v>
       </c>
       <c r="T95">
-        <v>14.78881928909185</v>
+        <v>17.2536225039405</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2350663222429684</v>
+        <v>0.2325656166871922</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2809218400538407</v>
+        <v>0.2828218400538408</v>
       </c>
       <c r="C96">
-        <v>-22.18526369632139</v>
+        <v>-23.64203616272371</v>
       </c>
       <c r="D96">
-        <v>9.667056303678615</v>
+        <v>9.589563837276289</v>
       </c>
       <c r="E96">
-        <v>128.72432</v>
+        <v>130.1036</v>
       </c>
       <c r="F96">
-        <v>129.65232</v>
+        <v>131.0316</v>
       </c>
       <c r="G96">
         <v>97.8</v>
@@ -9159,28 +9159,28 @@
         <v>7.11</v>
       </c>
       <c r="M96">
-        <v>30.572017056</v>
+        <v>30.89725128</v>
       </c>
       <c r="N96">
-        <v>-23.462017056</v>
+        <v>-23.78725128</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-23.462017056</v>
+        <v>-23.78725128</v>
       </c>
       <c r="Q96">
-        <v>-19.072017056</v>
+        <v>-19.39725128</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9878306675640132</v>
+        <v>1.176236801076817</v>
       </c>
       <c r="T96">
-        <v>17.2536225039405</v>
+        <v>20.70434700472861</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2325656166871922</v>
+        <v>0.2301175575641692</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2828218400538408</v>
+        <v>0.2847218400538408</v>
       </c>
       <c r="C97">
-        <v>-23.64203616272371</v>
+        <v>-25.09757612827029</v>
       </c>
       <c r="D97">
-        <v>9.589563837276289</v>
+        <v>9.513303871729738</v>
       </c>
       <c r="E97">
-        <v>130.1036</v>
+        <v>131.48288</v>
       </c>
       <c r="F97">
-        <v>131.0316</v>
+        <v>132.41088</v>
       </c>
       <c r="G97">
         <v>97.8</v>
@@ -9241,28 +9241,28 @@
         <v>7.11</v>
       </c>
       <c r="M97">
-        <v>30.89725128</v>
+        <v>31.22248550400001</v>
       </c>
       <c r="N97">
-        <v>-23.78725128</v>
+        <v>-24.11248550400001</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-23.78725128</v>
+        <v>-24.11248550400001</v>
       </c>
       <c r="Q97">
-        <v>-19.39725128</v>
+        <v>-19.72248550400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.176236801076817</v>
+        <v>1.458846001346021</v>
       </c>
       <c r="T97">
-        <v>20.70434700472861</v>
+        <v>25.88043375591077</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2301175575641692</v>
+        <v>0.2277204996728757</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2847218400538408</v>
+        <v>0.2866218400538408</v>
       </c>
       <c r="C98">
-        <v>-25.09757612827026</v>
+        <v>-26.5519127649617</v>
       </c>
       <c r="D98">
-        <v>9.513303871729738</v>
+        <v>9.43824723503829</v>
       </c>
       <c r="E98">
-        <v>131.48288</v>
+        <v>132.86216</v>
       </c>
       <c r="F98">
-        <v>132.41088</v>
+        <v>133.79016</v>
       </c>
       <c r="G98">
         <v>97.8</v>
@@ -9323,28 +9323,28 @@
         <v>7.11</v>
       </c>
       <c r="M98">
-        <v>31.222485504</v>
+        <v>31.547719728</v>
       </c>
       <c r="N98">
-        <v>-24.112485504</v>
+        <v>-24.437719728</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-24.112485504</v>
+        <v>-24.437719728</v>
       </c>
       <c r="Q98">
-        <v>-19.722485504</v>
+        <v>-20.047719728</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.458846001346018</v>
+        <v>1.929861335128023</v>
       </c>
       <c r="T98">
-        <v>25.8804337559107</v>
+        <v>34.50724500788094</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2277204996728758</v>
+        <v>0.2253728656556296</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2866218400538408</v>
+        <v>0.2885218400538407</v>
       </c>
       <c r="C99">
-        <v>-26.5519127649617</v>
+        <v>-28.00507433137781</v>
       </c>
       <c r="D99">
-        <v>9.43824723503829</v>
+        <v>9.364365668622204</v>
       </c>
       <c r="E99">
-        <v>132.86216</v>
+        <v>134.24144</v>
       </c>
       <c r="F99">
-        <v>133.79016</v>
+        <v>135.16944</v>
       </c>
       <c r="G99">
         <v>97.8</v>
@@ -9405,28 +9405,28 @@
         <v>7.11</v>
       </c>
       <c r="M99">
-        <v>31.547719728</v>
+        <v>31.872953952</v>
       </c>
       <c r="N99">
-        <v>-24.437719728</v>
+        <v>-24.762953952</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-24.437719728</v>
+        <v>-24.762953952</v>
       </c>
       <c r="Q99">
-        <v>-20.047719728</v>
+        <v>-20.372953952</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.929861335128023</v>
+        <v>2.871892002692035</v>
       </c>
       <c r="T99">
-        <v>34.50724500788094</v>
+        <v>51.76086751182141</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2253728656556296</v>
+        <v>0.2230731425366945</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2885218400538407</v>
+        <v>0.2904218400538408</v>
       </c>
       <c r="C100">
-        <v>-28.00507433137781</v>
+        <v>-29.45708820815048</v>
       </c>
       <c r="D100">
-        <v>9.364365668622204</v>
+        <v>9.291631791849523</v>
       </c>
       <c r="E100">
-        <v>134.24144</v>
+        <v>135.62072</v>
       </c>
       <c r="F100">
-        <v>135.16944</v>
+        <v>136.54872</v>
       </c>
       <c r="G100">
         <v>97.8</v>
@@ -9487,28 +9487,28 @@
         <v>7.11</v>
       </c>
       <c r="M100">
-        <v>31.872953952</v>
+        <v>32.198188176</v>
       </c>
       <c r="N100">
-        <v>-24.762953952</v>
+        <v>-25.088188176</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-24.762953952</v>
+        <v>-25.088188176</v>
       </c>
       <c r="Q100">
-        <v>-20.372953952</v>
+        <v>-20.698188176</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.871892002692035</v>
+        <v>5.69798400538407</v>
       </c>
       <c r="T100">
-        <v>51.76086751182141</v>
+        <v>103.5217350236428</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2230731425366945</v>
+        <v>0.2208198784706674</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2904218400538408</v>
-      </c>
-      <c r="C101">
-        <v>-29.45708820815048</v>
-      </c>
-      <c r="D101">
-        <v>9.291631791849523</v>
-      </c>
-      <c r="E101">
-        <v>135.62072</v>
-      </c>
-      <c r="F101">
-        <v>136.54872</v>
-      </c>
-      <c r="G101">
-        <v>97.8</v>
-      </c>
-      <c r="H101">
-        <v>137</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.5</v>
-      </c>
-      <c r="K101">
-        <v>4.39</v>
-      </c>
-      <c r="L101">
-        <v>7.11</v>
-      </c>
-      <c r="M101">
-        <v>32.198188176</v>
-      </c>
-      <c r="N101">
-        <v>-25.088188176</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-25.088188176</v>
-      </c>
-      <c r="Q101">
-        <v>-20.698188176</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.69798400538407</v>
-      </c>
-      <c r="T101">
-        <v>103.5217350236428</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2208198784706674</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
